--- a/june 2026/STT Report Elite Marketing (20-06-26) (1).xlsx
+++ b/june 2026/STT Report Elite Marketing (20-06-26) (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\june 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3ED7C7-AB94-4F99-B336-00F2A18E79DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B97DF1D-E414-4821-B1B7-96792AA30571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -2593,22 +2593,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2620,11 +2623,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2643,9 +2646,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2965,6 +2965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AP431"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3007,114 +3008,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="105" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="105" t="s">
+      <c r="A1" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="102" t="s">
+      <c r="C1" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="102" t="s">
+      <c r="D1" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="102" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="102" t="s">
+      <c r="E1" s="108" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="105" t="s">
+      <c r="G1" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="102" t="s">
+      <c r="H1" s="108" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="56"/>
-      <c r="K1" s="105" t="s">
+      <c r="K1" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="103" t="s">
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="104"/>
-      <c r="Q1" s="104"/>
-      <c r="R1" s="104"/>
-      <c r="S1" s="108" t="s">
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="110" t="s">
+      <c r="T1" s="111" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="110"/>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110" t="s">
+      <c r="U1" s="111"/>
+      <c r="V1" s="111"/>
+      <c r="W1" s="111"/>
+      <c r="X1" s="111" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="110"/>
-      <c r="AB1" s="106" t="s">
+      <c r="Y1" s="111"/>
+      <c r="Z1" s="111"/>
+      <c r="AA1" s="111"/>
+      <c r="AB1" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="106" t="s">
+      <c r="AC1" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="106" t="s">
+      <c r="AD1" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="106" t="s">
+      <c r="AE1" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="106" t="s">
+      <c r="AF1" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="106" t="s">
+      <c r="AG1" s="105" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="65">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="106" t="s">
+      <c r="AI1" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="106" t="s">
+      <c r="AJ1" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="106" t="s">
+      <c r="AK1" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="106" t="s">
+      <c r="AL1" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="106" t="s">
+      <c r="AM1" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="111" t="s">
+      <c r="AN1" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="111" t="s">
+      <c r="AO1" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="106" t="s">
+      <c r="AP1" s="105" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="105"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="102"/>
+    <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="107"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="108"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -3145,7 +3146,7 @@
       <c r="R2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="109"/>
+      <c r="S2" s="110"/>
       <c r="T2" s="4" t="s">
         <v>353</v>
       </c>
@@ -3170,25 +3171,25 @@
       <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="107"/>
-      <c r="AC2" s="107"/>
-      <c r="AD2" s="107"/>
-      <c r="AE2" s="107"/>
-      <c r="AF2" s="107"/>
-      <c r="AG2" s="107"/>
+      <c r="AB2" s="106"/>
+      <c r="AC2" s="106"/>
+      <c r="AD2" s="106"/>
+      <c r="AE2" s="106"/>
+      <c r="AF2" s="106"/>
+      <c r="AG2" s="106"/>
       <c r="AH2" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="107"/>
-      <c r="AJ2" s="107"/>
-      <c r="AK2" s="107"/>
-      <c r="AL2" s="107"/>
-      <c r="AM2" s="107"/>
-      <c r="AN2" s="112"/>
-      <c r="AO2" s="112"/>
-      <c r="AP2" s="107"/>
+      <c r="AI2" s="106"/>
+      <c r="AJ2" s="106"/>
+      <c r="AK2" s="106"/>
+      <c r="AL2" s="106"/>
+      <c r="AM2" s="106"/>
+      <c r="AN2" s="104"/>
+      <c r="AO2" s="104"/>
+      <c r="AP2" s="106"/>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="71">
         <v>46174</v>
       </c>
@@ -3325,7 +3326,7 @@
       <c r="AO3" s="6"/>
       <c r="AP3" s="12"/>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="71">
         <v>46174</v>
       </c>
@@ -3462,7 +3463,7 @@
       <c r="AO4" s="6"/>
       <c r="AP4" s="12"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="71">
         <v>46174</v>
       </c>
@@ -3599,7 +3600,7 @@
       <c r="AO5" s="6"/>
       <c r="AP5" s="12"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="71">
         <v>46174</v>
       </c>
@@ -4017,7 +4018,7 @@
       <c r="AN8"/>
       <c r="AP8" s="12"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="71">
         <v>46175</v>
       </c>
@@ -4152,7 +4153,7 @@
       <c r="AN9"/>
       <c r="AP9" s="12"/>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="71">
         <v>46175</v>
       </c>
@@ -4286,7 +4287,7 @@
       </c>
       <c r="AP10" s="12"/>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="71">
         <v>46175</v>
       </c>
@@ -4420,7 +4421,7 @@
       </c>
       <c r="AP11" s="12"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="71">
         <v>46175</v>
       </c>
@@ -4822,7 +4823,7 @@
       </c>
       <c r="AP14" s="12"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="71">
         <v>46176</v>
       </c>
@@ -4956,7 +4957,7 @@
       </c>
       <c r="AP15" s="12"/>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="71">
         <v>46176</v>
       </c>
@@ -5090,7 +5091,7 @@
       </c>
       <c r="AP16" s="12"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="71">
         <v>46176</v>
       </c>
@@ -5224,7 +5225,7 @@
       </c>
       <c r="AP17" s="12"/>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="71">
         <v>46176</v>
       </c>
@@ -5358,7 +5359,7 @@
       </c>
       <c r="AP18" s="12"/>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="71">
         <v>46176</v>
       </c>
@@ -5492,7 +5493,7 @@
       </c>
       <c r="AP19" s="12"/>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="71">
         <v>46176</v>
       </c>
@@ -5626,7 +5627,7 @@
       </c>
       <c r="AP20" s="12"/>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="71">
         <v>46176</v>
       </c>
@@ -5760,7 +5761,7 @@
       </c>
       <c r="AP21" s="12"/>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="71">
         <v>46176</v>
       </c>
@@ -5894,7 +5895,7 @@
       </c>
       <c r="AP22" s="12"/>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="71">
         <v>46176</v>
       </c>
@@ -6028,7 +6029,7 @@
       </c>
       <c r="AP23" s="12"/>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="71">
         <v>46177</v>
       </c>
@@ -6162,7 +6163,7 @@
       </c>
       <c r="AP24" s="12"/>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="71">
         <v>46177</v>
       </c>
@@ -6296,7 +6297,7 @@
       </c>
       <c r="AP25" s="12"/>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="71">
         <v>46177</v>
       </c>
@@ -6430,7 +6431,7 @@
       </c>
       <c r="AP26" s="12"/>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="71">
         <v>46177</v>
       </c>
@@ -6564,7 +6565,7 @@
       </c>
       <c r="AP27" s="12"/>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="71">
         <v>46177</v>
       </c>
@@ -6698,7 +6699,7 @@
       </c>
       <c r="AP28" s="12"/>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="71">
         <v>46178</v>
       </c>
@@ -6832,7 +6833,7 @@
       </c>
       <c r="AP29" s="12"/>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="71">
         <v>46178</v>
       </c>
@@ -6966,7 +6967,7 @@
       </c>
       <c r="AP30" s="12"/>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="71">
         <v>46178</v>
       </c>
@@ -7100,7 +7101,7 @@
       </c>
       <c r="AP31" s="12"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="71">
         <v>46178</v>
       </c>
@@ -7234,7 +7235,7 @@
       </c>
       <c r="AP32" s="12"/>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="71">
         <v>46178</v>
       </c>
@@ -7368,7 +7369,7 @@
       </c>
       <c r="AP33" s="12"/>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="71">
         <v>46178</v>
       </c>
@@ -7502,7 +7503,7 @@
       </c>
       <c r="AP34" s="12"/>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="71">
         <v>46209</v>
       </c>
@@ -7636,7 +7637,7 @@
       </c>
       <c r="AP35" s="12"/>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="71">
         <v>46209</v>
       </c>
@@ -7770,7 +7771,7 @@
       </c>
       <c r="AP36" s="12"/>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="71">
         <v>46209</v>
       </c>
@@ -7904,7 +7905,7 @@
       </c>
       <c r="AP37" s="12"/>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="71">
         <v>46209</v>
       </c>
@@ -8038,7 +8039,7 @@
       </c>
       <c r="AP38" s="12"/>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="71">
         <v>46209</v>
       </c>
@@ -8172,7 +8173,7 @@
       </c>
       <c r="AP39" s="12"/>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="71">
         <v>46209</v>
       </c>
@@ -8306,7 +8307,7 @@
       </c>
       <c r="AP40" s="12"/>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="71">
         <v>46209</v>
       </c>
@@ -8440,7 +8441,7 @@
       </c>
       <c r="AP41" s="12"/>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="71">
         <v>46211</v>
       </c>
@@ -8572,7 +8573,7 @@
       </c>
       <c r="AP42" s="12"/>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="71">
         <v>46211</v>
       </c>
@@ -8704,7 +8705,7 @@
       </c>
       <c r="AP43" s="12"/>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="71">
         <v>46211</v>
       </c>
@@ -8836,7 +8837,7 @@
       </c>
       <c r="AP44" s="12"/>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="71">
         <v>46211</v>
       </c>
@@ -8968,7 +8969,7 @@
       </c>
       <c r="AP45" s="12"/>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="71">
         <v>46211</v>
       </c>
@@ -9100,7 +9101,7 @@
       </c>
       <c r="AP46" s="12"/>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="71">
         <v>46211</v>
       </c>
@@ -9752,7 +9753,7 @@
       </c>
       <c r="AP51" s="12"/>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="71">
         <v>46212</v>
       </c>
@@ -9886,7 +9887,7 @@
       </c>
       <c r="AP52" s="12"/>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="71">
         <v>46212</v>
       </c>
@@ -10016,7 +10017,7 @@
       </c>
       <c r="AP53" s="12"/>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="71">
         <v>46212</v>
       </c>
@@ -10150,7 +10151,7 @@
       </c>
       <c r="AP54" s="12"/>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="71">
         <v>46212</v>
       </c>
@@ -10954,7 +10955,7 @@
       </c>
       <c r="AP60" s="12"/>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="71">
         <v>46212</v>
       </c>
@@ -11086,7 +11087,7 @@
       </c>
       <c r="AP61" s="12"/>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="71">
         <v>46212</v>
       </c>
@@ -11218,7 +11219,7 @@
       </c>
       <c r="AP62" s="12"/>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="71">
         <v>46212</v>
       </c>
@@ -11352,7 +11353,7 @@
       </c>
       <c r="AP63" s="12"/>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="71">
         <v>46212</v>
       </c>
@@ -11486,7 +11487,7 @@
       </c>
       <c r="AP64" s="12"/>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="71">
         <v>46212</v>
       </c>
@@ -11620,7 +11621,7 @@
       </c>
       <c r="AP65" s="12"/>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="71">
         <v>46212</v>
       </c>
@@ -11754,7 +11755,7 @@
       </c>
       <c r="AP66" s="12"/>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="71">
         <v>46212</v>
       </c>
@@ -11888,7 +11889,7 @@
       </c>
       <c r="AP67" s="12"/>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="71">
         <v>46212</v>
       </c>
@@ -12022,7 +12023,7 @@
       </c>
       <c r="AP68" s="12"/>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="71">
         <v>46212</v>
       </c>
@@ -12156,7 +12157,7 @@
       </c>
       <c r="AP69" s="12"/>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="71">
         <v>46212</v>
       </c>
@@ -12290,7 +12291,7 @@
       </c>
       <c r="AP70" s="12"/>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="71">
         <v>46212</v>
       </c>
@@ -12424,7 +12425,7 @@
       </c>
       <c r="AP71" s="12"/>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="71">
         <v>46183</v>
       </c>
@@ -12558,7 +12559,7 @@
       </c>
       <c r="AP72" s="12"/>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="71">
         <v>46183</v>
       </c>
@@ -13094,7 +13095,7 @@
       </c>
       <c r="AP76" s="12"/>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="71">
         <v>46183</v>
       </c>
@@ -13226,7 +13227,7 @@
       </c>
       <c r="AP77" s="12"/>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="71">
         <v>46183</v>
       </c>
@@ -13358,7 +13359,7 @@
       </c>
       <c r="AP78" s="12"/>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="71">
         <v>46183</v>
       </c>
@@ -13490,7 +13491,7 @@
       </c>
       <c r="AP79" s="12"/>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="71">
         <v>46184</v>
       </c>
@@ -13624,7 +13625,7 @@
       </c>
       <c r="AP80" s="12"/>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="71">
         <v>46184</v>
       </c>
@@ -13758,7 +13759,7 @@
       </c>
       <c r="AP81" s="12"/>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="71">
         <v>46184</v>
       </c>
@@ -13892,7 +13893,7 @@
       </c>
       <c r="AP82" s="12"/>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="71">
         <v>46184</v>
       </c>
@@ -14026,7 +14027,7 @@
       </c>
       <c r="AP83" s="12"/>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="71">
         <v>46184</v>
       </c>
@@ -14160,7 +14161,7 @@
       </c>
       <c r="AP84" s="12"/>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="71">
         <v>46184</v>
       </c>
@@ -14294,7 +14295,7 @@
       </c>
       <c r="AP85" s="12"/>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="71">
         <v>46184</v>
       </c>
@@ -15098,7 +15099,7 @@
       </c>
       <c r="AP91" s="12"/>
     </row>
-    <row r="92" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="71">
         <v>46184</v>
       </c>
@@ -15230,7 +15231,7 @@
       </c>
       <c r="AP92" s="12"/>
     </row>
-    <row r="93" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="71">
         <v>46184</v>
       </c>
@@ -15362,7 +15363,7 @@
       </c>
       <c r="AP93" s="12"/>
     </row>
-    <row r="94" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="71">
         <v>46184</v>
       </c>
@@ -15490,7 +15491,7 @@
       </c>
       <c r="AP94" s="12"/>
     </row>
-    <row r="95" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="71">
         <v>46184</v>
       </c>
@@ -15622,7 +15623,7 @@
       </c>
       <c r="AP95" s="12"/>
     </row>
-    <row r="96" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="71">
         <v>46185</v>
       </c>
@@ -15756,7 +15757,7 @@
       </c>
       <c r="AP96" s="12"/>
     </row>
-    <row r="97" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="71">
         <v>46185</v>
       </c>
@@ -15890,7 +15891,7 @@
       </c>
       <c r="AP97" s="12"/>
     </row>
-    <row r="98" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="71">
         <v>46185</v>
       </c>
@@ -16024,7 +16025,7 @@
       </c>
       <c r="AP98" s="12"/>
     </row>
-    <row r="99" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="71">
         <v>46185</v>
       </c>
@@ -16158,7 +16159,7 @@
       </c>
       <c r="AP99" s="12"/>
     </row>
-    <row r="100" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="71">
         <v>46185</v>
       </c>
@@ -16962,7 +16963,7 @@
       </c>
       <c r="AP105" s="12"/>
     </row>
-    <row r="106" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="71">
         <v>46185</v>
       </c>
@@ -17630,7 +17631,7 @@
       </c>
       <c r="AP110" s="12"/>
     </row>
-    <row r="111" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="71">
         <v>46186</v>
       </c>
@@ -17764,7 +17765,7 @@
       </c>
       <c r="AP111" s="12"/>
     </row>
-    <row r="112" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="71">
         <v>46186</v>
       </c>
@@ -17898,7 +17899,7 @@
       </c>
       <c r="AP112" s="12"/>
     </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="71">
         <v>46186</v>
       </c>
@@ -18032,7 +18033,7 @@
       </c>
       <c r="AP113" s="12"/>
     </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="71">
         <v>46186</v>
       </c>
@@ -18166,7 +18167,7 @@
       </c>
       <c r="AP114" s="12"/>
     </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="71">
         <v>46186</v>
       </c>
@@ -18300,7 +18301,7 @@
       </c>
       <c r="AP115" s="12"/>
     </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="71">
         <v>46186</v>
       </c>
@@ -18434,7 +18435,7 @@
       </c>
       <c r="AP116" s="12"/>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="71">
         <v>46186</v>
       </c>
@@ -18568,7 +18569,7 @@
       </c>
       <c r="AP117" s="12"/>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="71">
         <v>46186</v>
       </c>
@@ -18702,7 +18703,7 @@
       </c>
       <c r="AP118" s="12"/>
     </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="71">
         <v>46186</v>
       </c>
@@ -18836,7 +18837,7 @@
       </c>
       <c r="AP119" s="12"/>
     </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="71">
         <v>46186</v>
       </c>
@@ -18970,7 +18971,7 @@
       </c>
       <c r="AP120" s="12"/>
     </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="71">
         <v>46188</v>
       </c>
@@ -19104,7 +19105,7 @@
       </c>
       <c r="AP121" s="12"/>
     </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="71">
         <v>46188</v>
       </c>
@@ -19238,7 +19239,7 @@
       </c>
       <c r="AP122" s="12"/>
     </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="71">
         <v>46188</v>
       </c>
@@ -19372,7 +19373,7 @@
       </c>
       <c r="AP123" s="12"/>
     </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="71">
         <v>46188</v>
       </c>
@@ -19506,7 +19507,7 @@
       </c>
       <c r="AP124" s="12"/>
     </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="71">
         <v>46188</v>
       </c>
@@ -19640,7 +19641,7 @@
       </c>
       <c r="AP125" s="12"/>
     </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="71">
         <v>46188</v>
       </c>
@@ -19774,7 +19775,7 @@
       </c>
       <c r="AP126" s="12"/>
     </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="71">
         <v>46188</v>
       </c>
@@ -19908,7 +19909,7 @@
       </c>
       <c r="AP127" s="12"/>
     </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="71">
         <v>46188</v>
       </c>
@@ -20042,7 +20043,7 @@
       </c>
       <c r="AP128" s="12"/>
     </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="71">
         <v>46188</v>
       </c>
@@ -20176,7 +20177,7 @@
       </c>
       <c r="AP129" s="12"/>
     </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="71">
         <v>46188</v>
       </c>
@@ -20308,7 +20309,7 @@
       </c>
       <c r="AP130" s="12"/>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="71">
         <v>46188</v>
       </c>
@@ -20442,7 +20443,7 @@
       </c>
       <c r="AP131" s="12"/>
     </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="71">
         <v>46189</v>
       </c>
@@ -20574,7 +20575,7 @@
       </c>
       <c r="AP132" s="12"/>
     </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="71">
         <v>46189</v>
       </c>
@@ -20706,7 +20707,7 @@
       </c>
       <c r="AP133" s="12"/>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="71">
         <v>46189</v>
       </c>
@@ -20838,7 +20839,7 @@
       </c>
       <c r="AP134" s="12"/>
     </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="71">
         <v>46189</v>
       </c>
@@ -20970,7 +20971,7 @@
       </c>
       <c r="AP135" s="12"/>
     </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="71">
         <v>46189</v>
       </c>
@@ -21104,7 +21105,7 @@
       </c>
       <c r="AP136" s="12"/>
     </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="71">
         <v>46189</v>
       </c>
@@ -21238,7 +21239,7 @@
       </c>
       <c r="AP137" s="12"/>
     </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="71">
         <v>46189</v>
       </c>
@@ -21372,7 +21373,7 @@
       </c>
       <c r="AP138" s="12"/>
     </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="71">
         <v>46189</v>
       </c>
@@ -21506,7 +21507,7 @@
       </c>
       <c r="AP139" s="12"/>
     </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="71">
         <v>46189</v>
       </c>
@@ -21640,7 +21641,7 @@
       </c>
       <c r="AP140" s="12"/>
     </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="71">
         <v>46189</v>
       </c>
@@ -21774,7 +21775,7 @@
       </c>
       <c r="AP141" s="12"/>
     </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="71">
         <v>46189</v>
       </c>
@@ -21908,7 +21909,7 @@
       </c>
       <c r="AP142" s="12"/>
     </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="71">
         <v>46189</v>
       </c>
@@ -22042,7 +22043,7 @@
       </c>
       <c r="AP143" s="12"/>
     </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="71">
         <v>46189</v>
       </c>
@@ -23114,7 +23115,7 @@
       </c>
       <c r="AP151" s="12"/>
     </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="71">
         <v>46190</v>
       </c>
@@ -23248,7 +23249,7 @@
       </c>
       <c r="AP152" s="12"/>
     </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="71">
         <v>46190</v>
       </c>
@@ -23382,7 +23383,7 @@
       </c>
       <c r="AP153" s="12"/>
     </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="71">
         <v>46190</v>
       </c>
@@ -23514,7 +23515,7 @@
       </c>
       <c r="AP154" s="12"/>
     </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="71">
         <v>46190</v>
       </c>
@@ -23646,7 +23647,7 @@
       </c>
       <c r="AP155" s="12"/>
     </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="71">
         <v>46190</v>
       </c>
@@ -23778,7 +23779,7 @@
       </c>
       <c r="AP156" s="12"/>
     </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="71">
         <v>46190</v>
       </c>
@@ -23912,7 +23913,7 @@
       </c>
       <c r="AP157" s="12"/>
     </row>
-    <row r="158" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="71">
         <v>46190</v>
       </c>
@@ -24046,7 +24047,7 @@
       </c>
       <c r="AP158" s="12"/>
     </row>
-    <row r="159" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="71">
         <v>46190</v>
       </c>
@@ -24180,7 +24181,7 @@
       </c>
       <c r="AP159" s="12"/>
     </row>
-    <row r="160" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="71">
         <v>46190</v>
       </c>
@@ -24314,7 +24315,7 @@
       </c>
       <c r="AP160" s="12"/>
     </row>
-    <row r="161" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="71">
         <v>46190</v>
       </c>
@@ -24446,7 +24447,7 @@
       </c>
       <c r="AP161" s="12"/>
     </row>
-    <row r="162" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="71">
         <v>46190</v>
       </c>
@@ -24578,7 +24579,7 @@
       </c>
       <c r="AP162" s="12"/>
     </row>
-    <row r="163" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="71">
         <v>46190</v>
       </c>
@@ -24710,7 +24711,7 @@
       </c>
       <c r="AP163" s="12"/>
     </row>
-    <row r="164" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="71">
         <v>46190</v>
       </c>
@@ -24842,7 +24843,7 @@
       </c>
       <c r="AP164" s="12"/>
     </row>
-    <row r="165" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="71">
         <v>46190</v>
       </c>
@@ -24974,7 +24975,7 @@
       </c>
       <c r="AP165" s="12"/>
     </row>
-    <row r="166" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="71">
         <v>46190</v>
       </c>
@@ -25106,7 +25107,7 @@
       </c>
       <c r="AP166" s="12"/>
     </row>
-    <row r="167" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="71">
         <v>46190</v>
       </c>
@@ -25238,7 +25239,7 @@
       </c>
       <c r="AP167" s="12"/>
     </row>
-    <row r="168" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="71">
         <v>46190</v>
       </c>
@@ -25370,7 +25371,7 @@
       </c>
       <c r="AP168" s="12"/>
     </row>
-    <row r="169" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="71">
         <v>46190</v>
       </c>
@@ -25502,7 +25503,7 @@
       </c>
       <c r="AP169" s="12"/>
     </row>
-    <row r="170" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="71">
         <v>46190</v>
       </c>
@@ -25634,7 +25635,7 @@
       </c>
       <c r="AP170" s="12"/>
     </row>
-    <row r="171" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="71">
         <v>46190</v>
       </c>
@@ -25766,7 +25767,7 @@
       </c>
       <c r="AP171" s="12"/>
     </row>
-    <row r="172" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="71">
         <v>46190</v>
       </c>
@@ -25898,7 +25899,7 @@
       </c>
       <c r="AP172" s="12"/>
     </row>
-    <row r="173" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="71">
         <v>46190</v>
       </c>
@@ -26030,7 +26031,7 @@
       </c>
       <c r="AP173" s="12"/>
     </row>
-    <row r="174" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="71">
         <v>46190</v>
       </c>
@@ -26162,7 +26163,7 @@
       </c>
       <c r="AP174" s="12"/>
     </row>
-    <row r="175" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="71">
         <v>46190</v>
       </c>
@@ -26294,7 +26295,7 @@
       </c>
       <c r="AP175" s="12"/>
     </row>
-    <row r="176" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="71">
         <v>46190</v>
       </c>
@@ -26426,7 +26427,7 @@
       </c>
       <c r="AP176" s="12"/>
     </row>
-    <row r="177" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="71">
         <v>46191</v>
       </c>
@@ -26560,7 +26561,7 @@
       </c>
       <c r="AP177" s="12"/>
     </row>
-    <row r="178" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="71">
         <v>46191</v>
       </c>
@@ -26694,7 +26695,7 @@
       </c>
       <c r="AP178" s="12"/>
     </row>
-    <row r="179" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="71">
         <v>46191</v>
       </c>
@@ -26828,7 +26829,7 @@
       </c>
       <c r="AP179" s="12"/>
     </row>
-    <row r="180" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="71">
         <v>46191</v>
       </c>
@@ -26962,7 +26963,7 @@
       </c>
       <c r="AP180" s="12"/>
     </row>
-    <row r="181" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="71">
         <v>46191</v>
       </c>
@@ -27096,7 +27097,7 @@
       </c>
       <c r="AP181" s="12"/>
     </row>
-    <row r="182" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="71">
         <v>46191</v>
       </c>
@@ -27230,7 +27231,7 @@
       </c>
       <c r="AP182" s="12"/>
     </row>
-    <row r="183" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="71">
         <v>46191</v>
       </c>
@@ -27364,7 +27365,7 @@
       </c>
       <c r="AP183" s="12"/>
     </row>
-    <row r="184" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="71">
         <v>46191</v>
       </c>
@@ -27498,7 +27499,7 @@
       </c>
       <c r="AP184" s="12"/>
     </row>
-    <row r="185" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="71">
         <v>46191</v>
       </c>
@@ -27632,7 +27633,7 @@
       </c>
       <c r="AP185" s="12"/>
     </row>
-    <row r="186" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="71">
         <v>46191</v>
       </c>
@@ -27766,7 +27767,7 @@
       </c>
       <c r="AP186" s="12"/>
     </row>
-    <row r="187" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="71">
         <v>46191</v>
       </c>
@@ -27898,7 +27899,7 @@
       </c>
       <c r="AP187" s="12"/>
     </row>
-    <row r="188" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="71">
         <v>46191</v>
       </c>
@@ -28030,7 +28031,7 @@
       </c>
       <c r="AP188" s="12"/>
     </row>
-    <row r="189" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="71">
         <v>46191</v>
       </c>
@@ -28162,7 +28163,7 @@
       </c>
       <c r="AP189" s="12"/>
     </row>
-    <row r="190" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="71">
         <v>46191</v>
       </c>
@@ -28294,7 +28295,7 @@
       </c>
       <c r="AP190" s="12"/>
     </row>
-    <row r="191" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="71">
         <v>46191</v>
       </c>
@@ -28426,7 +28427,7 @@
       </c>
       <c r="AP191" s="12"/>
     </row>
-    <row r="192" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="71">
         <v>46191</v>
       </c>
@@ -28558,7 +28559,7 @@
       </c>
       <c r="AP192" s="12"/>
     </row>
-    <row r="193" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="71">
         <v>46191</v>
       </c>
@@ -28690,7 +28691,7 @@
       </c>
       <c r="AP193" s="12"/>
     </row>
-    <row r="194" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="71">
         <v>46191</v>
       </c>
@@ -28822,7 +28823,7 @@
       </c>
       <c r="AP194" s="12"/>
     </row>
-    <row r="195" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="71">
         <v>46191</v>
       </c>
@@ -28954,7 +28955,7 @@
       </c>
       <c r="AP195" s="12"/>
     </row>
-    <row r="196" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="71">
         <v>46191</v>
       </c>
@@ -29086,7 +29087,7 @@
       </c>
       <c r="AP196" s="12"/>
     </row>
-    <row r="197" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="71">
         <v>46191</v>
       </c>
@@ -29218,7 +29219,7 @@
       </c>
       <c r="AP197" s="12"/>
     </row>
-    <row r="198" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="71">
         <v>46191</v>
       </c>
@@ -29350,7 +29351,7 @@
       </c>
       <c r="AP198" s="12"/>
     </row>
-    <row r="199" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="71">
         <v>46191</v>
       </c>
@@ -29482,7 +29483,7 @@
       </c>
       <c r="AP199" s="12"/>
     </row>
-    <row r="200" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="71">
         <v>46191</v>
       </c>
@@ -29614,7 +29615,7 @@
       </c>
       <c r="AP200" s="12"/>
     </row>
-    <row r="201" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="71">
         <v>46191</v>
       </c>
@@ -29746,7 +29747,7 @@
       </c>
       <c r="AP201" s="12"/>
     </row>
-    <row r="202" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="71">
         <v>46191</v>
       </c>
@@ -29878,7 +29879,7 @@
       </c>
       <c r="AP202" s="12"/>
     </row>
-    <row r="203" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="71">
         <v>46191</v>
       </c>
@@ -30010,7 +30011,7 @@
       </c>
       <c r="AP203" s="12"/>
     </row>
-    <row r="204" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="71">
         <v>46191</v>
       </c>
@@ -30142,7 +30143,7 @@
       </c>
       <c r="AP204" s="12"/>
     </row>
-    <row r="205" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="71">
         <v>46191</v>
       </c>
@@ -30274,7 +30275,7 @@
       </c>
       <c r="AP205" s="12"/>
     </row>
-    <row r="206" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="71">
         <v>46191</v>
       </c>
@@ -30406,7 +30407,7 @@
       </c>
       <c r="AP206" s="12"/>
     </row>
-    <row r="207" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="71">
         <v>46192</v>
       </c>
@@ -30538,7 +30539,7 @@
       </c>
       <c r="AP207" s="12"/>
     </row>
-    <row r="208" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="71">
         <v>46192</v>
       </c>
@@ -30670,7 +30671,7 @@
       </c>
       <c r="AP208" s="12"/>
     </row>
-    <row r="209" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="71">
         <v>46192</v>
       </c>
@@ -30804,7 +30805,7 @@
       </c>
       <c r="AP209" s="12"/>
     </row>
-    <row r="210" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="71">
         <v>46192</v>
       </c>
@@ -30936,7 +30937,7 @@
       </c>
       <c r="AP210" s="12"/>
     </row>
-    <row r="211" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="71">
         <v>46192</v>
       </c>
@@ -31332,7 +31333,7 @@
       </c>
       <c r="AP213" s="12"/>
     </row>
-    <row r="214" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="71">
         <v>46192</v>
       </c>
@@ -31464,7 +31465,7 @@
       </c>
       <c r="AP214" s="12"/>
     </row>
-    <row r="215" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="71">
         <v>46192</v>
       </c>
@@ -31596,7 +31597,7 @@
       </c>
       <c r="AP215" s="12"/>
     </row>
-    <row r="216" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="71">
         <v>46192</v>
       </c>
@@ -31728,7 +31729,7 @@
       </c>
       <c r="AP216" s="12"/>
     </row>
-    <row r="217" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="71">
         <v>46192</v>
       </c>
@@ -31860,7 +31861,7 @@
       </c>
       <c r="AP217" s="12"/>
     </row>
-    <row r="218" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="71">
         <v>46192</v>
       </c>
@@ -31992,7 +31993,7 @@
       </c>
       <c r="AP218" s="12"/>
     </row>
-    <row r="219" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="71">
         <v>46192</v>
       </c>
@@ -32124,7 +32125,7 @@
       </c>
       <c r="AP219" s="12"/>
     </row>
-    <row r="220" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="71">
         <v>46192</v>
       </c>
@@ -32256,7 +32257,7 @@
       </c>
       <c r="AP220" s="12"/>
     </row>
-    <row r="221" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="71">
         <v>46192</v>
       </c>
@@ -32388,7 +32389,7 @@
       </c>
       <c r="AP221" s="12"/>
     </row>
-    <row r="222" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="71">
         <v>46192</v>
       </c>
@@ -32520,7 +32521,7 @@
       </c>
       <c r="AP222" s="12"/>
     </row>
-    <row r="223" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="71">
         <v>46192</v>
       </c>
@@ -32652,7 +32653,7 @@
       </c>
       <c r="AP223" s="12"/>
     </row>
-    <row r="224" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="71">
         <v>46192</v>
       </c>
@@ -32784,7 +32785,7 @@
       </c>
       <c r="AP224" s="12"/>
     </row>
-    <row r="225" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="71">
         <v>46192</v>
       </c>
@@ -32916,7 +32917,7 @@
       </c>
       <c r="AP225" s="12"/>
     </row>
-    <row r="226" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="71">
         <v>46192</v>
       </c>
@@ -33048,7 +33049,7 @@
       </c>
       <c r="AP226" s="12"/>
     </row>
-    <row r="227" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="71">
         <v>46192</v>
       </c>
@@ -33180,7 +33181,7 @@
       </c>
       <c r="AP227" s="12"/>
     </row>
-    <row r="228" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="71">
         <v>46192</v>
       </c>
@@ -34116,7 +34117,7 @@
       </c>
       <c r="AP234" s="12"/>
     </row>
-    <row r="235" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="71">
         <v>46193</v>
       </c>
@@ -34250,7 +34251,7 @@
       </c>
       <c r="AP235" s="12"/>
     </row>
-    <row r="236" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="71">
         <v>46193</v>
       </c>
@@ -34384,7 +34385,7 @@
       </c>
       <c r="AP236" s="12"/>
     </row>
-    <row r="237" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="71">
         <v>46193</v>
       </c>
@@ -34518,7 +34519,7 @@
       </c>
       <c r="AP237" s="12"/>
     </row>
-    <row r="238" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="71">
         <v>46193</v>
       </c>
@@ -34652,7 +34653,7 @@
       </c>
       <c r="AP238" s="12"/>
     </row>
-    <row r="239" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="71">
         <v>46193</v>
       </c>
@@ -34786,7 +34787,7 @@
       </c>
       <c r="AP239" s="12"/>
     </row>
-    <row r="240" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="71">
         <v>46193</v>
       </c>
@@ -34920,7 +34921,7 @@
       </c>
       <c r="AP240" s="12"/>
     </row>
-    <row r="241" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="71">
         <v>46193</v>
       </c>
@@ -35054,7 +35055,7 @@
       </c>
       <c r="AP241" s="12"/>
     </row>
-    <row r="242" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="71">
         <v>46193</v>
       </c>
@@ -35188,7 +35189,7 @@
       </c>
       <c r="AP242" s="12"/>
     </row>
-    <row r="243" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="71">
         <v>46193</v>
       </c>
@@ -35322,7 +35323,7 @@
       </c>
       <c r="AP243" s="12"/>
     </row>
-    <row r="244" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="71">
         <v>46193</v>
       </c>
@@ -35456,7 +35457,7 @@
       </c>
       <c r="AP244" s="12"/>
     </row>
-    <row r="245" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="71">
         <v>46193</v>
       </c>
@@ -35590,7 +35591,7 @@
       </c>
       <c r="AP245" s="12"/>
     </row>
-    <row r="246" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="71">
         <v>46193</v>
       </c>
@@ -35724,7 +35725,7 @@
       </c>
       <c r="AP246" s="12"/>
     </row>
-    <row r="247" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="71">
         <v>46193</v>
       </c>
@@ -35858,7 +35859,7 @@
       </c>
       <c r="AP247" s="12"/>
     </row>
-    <row r="248" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="71">
         <v>46193</v>
       </c>
@@ -35992,7 +35993,7 @@
       </c>
       <c r="AP248" s="12"/>
     </row>
-    <row r="249" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="71">
         <v>46193</v>
       </c>
@@ -36126,7 +36127,7 @@
       </c>
       <c r="AP249" s="12"/>
     </row>
-    <row r="250" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="71">
         <v>46193</v>
       </c>
@@ -36256,7 +36257,7 @@
       </c>
       <c r="AP250" s="12"/>
     </row>
-    <row r="251" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="71">
         <v>46193</v>
       </c>
@@ -36388,7 +36389,7 @@
       </c>
       <c r="AP251" s="12"/>
     </row>
-    <row r="252" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="71">
         <v>46195</v>
       </c>
@@ -36514,7 +36515,7 @@
       </c>
       <c r="AP252" s="12"/>
     </row>
-    <row r="253" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="71">
         <v>46195</v>
       </c>
@@ -36640,7 +36641,7 @@
       </c>
       <c r="AP253" s="12"/>
     </row>
-    <row r="254" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="71">
         <v>46195</v>
       </c>
@@ -36772,7 +36773,7 @@
       </c>
       <c r="AP254" s="12"/>
     </row>
-    <row r="255" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="71">
         <v>46195</v>
       </c>
@@ -36894,7 +36895,7 @@
       </c>
       <c r="AP255" s="12"/>
     </row>
-    <row r="256" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="71">
         <v>46195</v>
       </c>
@@ -37026,7 +37027,7 @@
       </c>
       <c r="AP256" s="12"/>
     </row>
-    <row r="257" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="71">
         <v>46195</v>
       </c>
@@ -37152,7 +37153,7 @@
       </c>
       <c r="AP257" s="12"/>
     </row>
-    <row r="258" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="71">
         <v>46195</v>
       </c>
@@ -37278,7 +37279,7 @@
       </c>
       <c r="AP258" s="12"/>
     </row>
-    <row r="259" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="71">
         <v>46195</v>
       </c>
@@ -37410,7 +37411,7 @@
       </c>
       <c r="AP259" s="12"/>
     </row>
-    <row r="260" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="71">
         <v>46195</v>
       </c>
@@ -37534,7 +37535,7 @@
       </c>
       <c r="AP260" s="12"/>
     </row>
-    <row r="261" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="71">
         <v>46195</v>
       </c>
@@ -37656,7 +37657,7 @@
       </c>
       <c r="AP261" s="12"/>
     </row>
-    <row r="262" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="71">
         <v>46195</v>
       </c>
@@ -37780,7 +37781,7 @@
       </c>
       <c r="AP262" s="12"/>
     </row>
-    <row r="263" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="71">
         <v>46195</v>
       </c>
@@ -37906,7 +37907,7 @@
       </c>
       <c r="AP263" s="12"/>
     </row>
-    <row r="264" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="71">
         <v>46195</v>
       </c>
@@ -38032,7 +38033,7 @@
       </c>
       <c r="AP264" s="12"/>
     </row>
-    <row r="265" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="71">
         <v>46195</v>
       </c>
@@ -38158,7 +38159,7 @@
       </c>
       <c r="AP265" s="12"/>
     </row>
-    <row r="266" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="71">
         <v>46195</v>
       </c>
@@ -38280,7 +38281,7 @@
       </c>
       <c r="AP266" s="12"/>
     </row>
-    <row r="267" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="71">
         <v>46195</v>
       </c>
@@ -38412,7 +38413,7 @@
       </c>
       <c r="AP267" s="12"/>
     </row>
-    <row r="268" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="71">
         <v>46195</v>
       </c>
@@ -38536,7 +38537,7 @@
       </c>
       <c r="AP268" s="12"/>
     </row>
-    <row r="269" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="71">
         <v>46195</v>
       </c>
@@ -38662,7 +38663,7 @@
       </c>
       <c r="AP269" s="12"/>
     </row>
-    <row r="270" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="71">
         <v>46195</v>
       </c>
@@ -38788,7 +38789,7 @@
       </c>
       <c r="AP270" s="12"/>
     </row>
-    <row r="271" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="71">
         <v>46195</v>
       </c>
@@ -38920,7 +38921,7 @@
       </c>
       <c r="AP271" s="12"/>
     </row>
-    <row r="272" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="71">
         <v>46195</v>
       </c>
@@ -40038,7 +40039,7 @@
       </c>
       <c r="AP280" s="12"/>
     </row>
-    <row r="281" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="71">
         <v>46196</v>
       </c>
@@ -40160,7 +40161,7 @@
       </c>
       <c r="AP281" s="12"/>
     </row>
-    <row r="282" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="71">
         <v>46196</v>
       </c>
@@ -40286,7 +40287,7 @@
       </c>
       <c r="AP282" s="12"/>
     </row>
-    <row r="283" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="71">
         <v>46196</v>
       </c>
@@ -40418,7 +40419,7 @@
       </c>
       <c r="AP283" s="12"/>
     </row>
-    <row r="284" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="71">
         <v>46196</v>
       </c>
@@ -40544,7 +40545,7 @@
       </c>
       <c r="AP284" s="12"/>
     </row>
-    <row r="285" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="71">
         <v>46196</v>
       </c>
@@ -40672,7 +40673,7 @@
       </c>
       <c r="AP285" s="12"/>
     </row>
-    <row r="286" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="71">
         <v>46196</v>
       </c>
@@ -40798,7 +40799,7 @@
       </c>
       <c r="AP286" s="12"/>
     </row>
-    <row r="287" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="71">
         <v>46196</v>
       </c>
@@ -41932,7 +41933,7 @@
       </c>
       <c r="AP295" s="12"/>
     </row>
-    <row r="296" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="71">
         <v>46196</v>
       </c>
@@ -42058,7 +42059,7 @@
       </c>
       <c r="AP296" s="12"/>
     </row>
-    <row r="297" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="71">
         <v>46196</v>
       </c>
@@ -42190,7 +42191,7 @@
       </c>
       <c r="AP297" s="12"/>
     </row>
-    <row r="298" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="71">
         <v>46196</v>
       </c>
@@ -42312,7 +42313,7 @@
       </c>
       <c r="AP298" s="12"/>
     </row>
-    <row r="299" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="71">
         <v>46196</v>
       </c>
@@ -42434,7 +42435,7 @@
       </c>
       <c r="AP299" s="12"/>
     </row>
-    <row r="300" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="71">
         <v>46197</v>
       </c>
@@ -42558,7 +42559,7 @@
       </c>
       <c r="AP300" s="12"/>
     </row>
-    <row r="301" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="71">
         <v>46197</v>
       </c>
@@ -42686,7 +42687,7 @@
       </c>
       <c r="AP301" s="12"/>
     </row>
-    <row r="302" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="71">
         <v>46197</v>
       </c>
@@ -42814,7 +42815,7 @@
       </c>
       <c r="AP302" s="12"/>
     </row>
-    <row r="303" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="71">
         <v>46197</v>
       </c>
@@ -42940,7 +42941,7 @@
       </c>
       <c r="AP303" s="12"/>
     </row>
-    <row r="304" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="71">
         <v>46197</v>
       </c>
@@ -43066,7 +43067,7 @@
       </c>
       <c r="AP304" s="12"/>
     </row>
-    <row r="305" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="71">
         <v>46197</v>
       </c>
@@ -43188,7 +43189,7 @@
       </c>
       <c r="AP305" s="12"/>
     </row>
-    <row r="306" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="71">
         <v>46197</v>
       </c>
@@ -43320,7 +43321,7 @@
       </c>
       <c r="AP306" s="12"/>
     </row>
-    <row r="307" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="71">
         <v>46197</v>
       </c>
@@ -43444,7 +43445,7 @@
       </c>
       <c r="AP307" s="12"/>
     </row>
-    <row r="308" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="71">
         <v>46197</v>
       </c>
@@ -43576,7 +43577,7 @@
       </c>
       <c r="AP308" s="12"/>
     </row>
-    <row r="309" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="71">
         <v>46197</v>
       </c>
@@ -44818,7 +44819,7 @@
       </c>
       <c r="AP318" s="12"/>
     </row>
-    <row r="319" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="71">
         <v>46196</v>
       </c>
@@ -44948,7 +44949,7 @@
       </c>
       <c r="AP319" s="12"/>
     </row>
-    <row r="320" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="71">
         <v>46196</v>
       </c>
@@ -45078,7 +45079,7 @@
       </c>
       <c r="AP320" s="12"/>
     </row>
-    <row r="321" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="71">
         <v>46196</v>
       </c>
@@ -45208,7 +45209,7 @@
       </c>
       <c r="AP321" s="12"/>
     </row>
-    <row r="322" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="71">
         <v>46196</v>
       </c>
@@ -45338,7 +45339,7 @@
       </c>
       <c r="AP322" s="12"/>
     </row>
-    <row r="323" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="71">
         <v>46196</v>
       </c>
@@ -45468,7 +45469,7 @@
       </c>
       <c r="AP323" s="12"/>
     </row>
-    <row r="324" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="71">
         <v>46196</v>
       </c>
@@ -45598,7 +45599,7 @@
       </c>
       <c r="AP324" s="12"/>
     </row>
-    <row r="325" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="71">
         <v>46196</v>
       </c>
@@ -45728,7 +45729,7 @@
       </c>
       <c r="AP325" s="12"/>
     </row>
-    <row r="326" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="71">
         <v>46196</v>
       </c>
@@ -45858,7 +45859,7 @@
       </c>
       <c r="AP326" s="12"/>
     </row>
-    <row r="327" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="71">
         <v>46196</v>
       </c>
@@ -45988,7 +45989,7 @@
       </c>
       <c r="AP327" s="12"/>
     </row>
-    <row r="328" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="71">
         <v>46196</v>
       </c>
@@ -46118,7 +46119,7 @@
       </c>
       <c r="AP328" s="12"/>
     </row>
-    <row r="329" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="71">
         <v>46196</v>
       </c>
@@ -46248,7 +46249,7 @@
       </c>
       <c r="AP329" s="12"/>
     </row>
-    <row r="330" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="71">
         <v>46197</v>
       </c>
@@ -46380,7 +46381,7 @@
       </c>
       <c r="AP330" s="12"/>
     </row>
-    <row r="331" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="71">
         <v>46197</v>
       </c>
@@ -46510,7 +46511,7 @@
       </c>
       <c r="AP331" s="12"/>
     </row>
-    <row r="332" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="71">
         <v>46197</v>
       </c>
@@ -46640,7 +46641,7 @@
       </c>
       <c r="AP332" s="12"/>
     </row>
-    <row r="333" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="71">
         <v>46197</v>
       </c>
@@ -46766,7 +46767,7 @@
       </c>
       <c r="AP333" s="12"/>
     </row>
-    <row r="334" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="71">
         <v>46197</v>
       </c>
@@ -46896,7 +46897,7 @@
       </c>
       <c r="AP334" s="12"/>
     </row>
-    <row r="335" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="71">
         <v>46197</v>
       </c>
@@ -47026,7 +47027,7 @@
       </c>
       <c r="AP335" s="12"/>
     </row>
-    <row r="336" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="71">
         <v>46202</v>
       </c>
@@ -47154,7 +47155,7 @@
       </c>
       <c r="AP336" s="12"/>
     </row>
-    <row r="337" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="71">
         <v>46202</v>
       </c>
@@ -47278,7 +47279,7 @@
       </c>
       <c r="AP337" s="12"/>
     </row>
-    <row r="338" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="71">
         <v>46202</v>
       </c>
@@ -47404,7 +47405,7 @@
       </c>
       <c r="AP338" s="12"/>
     </row>
-    <row r="339" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="71">
         <v>46202</v>
       </c>
@@ -47528,7 +47529,7 @@
       </c>
       <c r="AP339" s="12"/>
     </row>
-    <row r="340" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="71">
         <v>46202</v>
       </c>
@@ -47658,7 +47659,7 @@
       </c>
       <c r="AP340" s="12"/>
     </row>
-    <row r="341" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="71">
         <v>46202</v>
       </c>
@@ -47784,7 +47785,7 @@
       </c>
       <c r="AP341" s="12"/>
     </row>
-    <row r="342" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="71">
         <v>46202</v>
       </c>
@@ -47910,7 +47911,7 @@
       </c>
       <c r="AP342" s="12"/>
     </row>
-    <row r="343" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="71">
         <v>46202</v>
       </c>
@@ -48034,7 +48035,7 @@
       </c>
       <c r="AP343" s="12"/>
     </row>
-    <row r="344" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="71">
         <v>46202</v>
       </c>
@@ -48160,7 +48161,7 @@
       </c>
       <c r="AP344" s="12"/>
     </row>
-    <row r="345" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="71">
         <v>46202</v>
       </c>
@@ -48286,7 +48287,7 @@
       </c>
       <c r="AP345" s="12"/>
     </row>
-    <row r="346" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="71">
         <v>46202</v>
       </c>
@@ -48412,7 +48413,7 @@
       </c>
       <c r="AP346" s="12"/>
     </row>
-    <row r="347" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="71">
         <v>46202</v>
       </c>
@@ -48790,7 +48791,7 @@
       </c>
       <c r="AP349" s="12"/>
     </row>
-    <row r="350" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="71">
         <v>46202</v>
       </c>
@@ -48920,7 +48921,7 @@
       </c>
       <c r="AP350" s="12"/>
     </row>
-    <row r="351" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="71">
         <v>46202</v>
       </c>
@@ -49050,7 +49051,7 @@
       </c>
       <c r="AP351" s="12"/>
     </row>
-    <row r="352" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="71">
         <v>46202</v>
       </c>
@@ -49170,7 +49171,7 @@
       </c>
       <c r="AP352" s="12"/>
     </row>
-    <row r="353" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="71">
         <v>46202</v>
       </c>
@@ -49300,7 +49301,7 @@
       </c>
       <c r="AP353" s="12"/>
     </row>
-    <row r="354" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="71">
         <v>46202</v>
       </c>
@@ -49430,7 +49431,7 @@
       </c>
       <c r="AP354" s="12"/>
     </row>
-    <row r="355" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="71">
         <v>46202</v>
       </c>
@@ -49560,7 +49561,7 @@
       </c>
       <c r="AP355" s="12"/>
     </row>
-    <row r="356" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="71">
         <v>46202</v>
       </c>
@@ -49690,7 +49691,7 @@
       </c>
       <c r="AP356" s="12"/>
     </row>
-    <row r="357" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="71">
         <v>46202</v>
       </c>
@@ -49820,7 +49821,7 @@
       </c>
       <c r="AP357" s="12"/>
     </row>
-    <row r="358" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="71">
         <v>46202</v>
       </c>
@@ -49950,7 +49951,7 @@
       </c>
       <c r="AP358" s="12"/>
     </row>
-    <row r="359" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="71">
         <v>46202</v>
       </c>
@@ -50080,7 +50081,7 @@
       </c>
       <c r="AP359" s="12"/>
     </row>
-    <row r="360" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="71">
         <v>46202</v>
       </c>
@@ -50210,7 +50211,7 @@
       </c>
       <c r="AP360" s="12"/>
     </row>
-    <row r="361" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="71">
         <v>46202</v>
       </c>
@@ -50340,7 +50341,7 @@
       </c>
       <c r="AP361" s="12"/>
     </row>
-    <row r="362" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="71">
         <v>46202</v>
       </c>
@@ -50470,7 +50471,7 @@
       </c>
       <c r="AP362" s="12"/>
     </row>
-    <row r="363" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="71">
         <v>46202</v>
       </c>
@@ -50596,7 +50597,7 @@
       </c>
       <c r="AP363" s="12"/>
     </row>
-    <row r="364" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="71">
         <v>46202</v>
       </c>
@@ -50726,7 +50727,7 @@
       </c>
       <c r="AP364" s="12"/>
     </row>
-    <row r="365" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="71">
         <v>46203</v>
       </c>
@@ -50852,7 +50853,7 @@
       </c>
       <c r="AP365" s="12"/>
     </row>
-    <row r="366" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="71">
         <v>46203</v>
       </c>
@@ -50974,7 +50975,7 @@
       </c>
       <c r="AP366" s="12"/>
     </row>
-    <row r="367" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="71">
         <v>46203</v>
       </c>
@@ -51102,7 +51103,7 @@
       </c>
       <c r="AP367" s="12"/>
     </row>
-    <row r="368" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="71">
         <v>46203</v>
       </c>
@@ -51228,7 +51229,7 @@
       </c>
       <c r="AP368" s="12"/>
     </row>
-    <row r="369" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="71">
         <v>46203</v>
       </c>
@@ -51352,7 +51353,7 @@
       </c>
       <c r="AP369" s="12"/>
     </row>
-    <row r="370" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="71">
         <v>46203</v>
       </c>
@@ -51474,7 +51475,7 @@
       </c>
       <c r="AP370" s="12"/>
     </row>
-    <row r="371" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="71">
         <v>46203</v>
       </c>
@@ -51604,7 +51605,7 @@
       </c>
       <c r="AP371" s="12"/>
     </row>
-    <row r="372" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="71">
         <v>46203</v>
       </c>
@@ -51726,7 +51727,7 @@
       </c>
       <c r="AP372" s="12"/>
     </row>
-    <row r="373" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="71">
         <v>46203</v>
       </c>
@@ -51848,7 +51849,7 @@
       </c>
       <c r="AP373" s="12"/>
     </row>
-    <row r="374" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="71">
         <v>46203</v>
       </c>
@@ -51974,7 +51975,7 @@
       </c>
       <c r="AP374" s="12"/>
     </row>
-    <row r="375" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="71">
         <v>46203</v>
       </c>
@@ -52096,7 +52097,7 @@
       </c>
       <c r="AP375" s="12"/>
     </row>
-    <row r="376" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="71">
         <v>46203</v>
       </c>
@@ -52218,7 +52219,7 @@
       </c>
       <c r="AP376" s="12"/>
     </row>
-    <row r="377" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="71">
         <v>46203</v>
       </c>
@@ -54470,7 +54471,7 @@
       </c>
       <c r="AP394" s="12"/>
     </row>
-    <row r="395" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" s="71">
         <v>46203</v>
       </c>
@@ -54489,7 +54490,7 @@
       <c r="F395" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G395" s="119" t="s">
+      <c r="G395" s="102" t="s">
         <v>328</v>
       </c>
       <c r="H395" s="19" t="s">
@@ -54600,7 +54601,7 @@
       </c>
       <c r="AP395" s="12"/>
     </row>
-    <row r="396" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" s="71">
         <v>46203</v>
       </c>
@@ -54619,7 +54620,7 @@
       <c r="F396" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G396" s="119" t="s">
+      <c r="G396" s="102" t="s">
         <v>328</v>
       </c>
       <c r="H396" s="19" t="s">
@@ -54730,7 +54731,7 @@
       </c>
       <c r="AP396" s="12"/>
     </row>
-    <row r="397" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" s="71">
         <v>46203</v>
       </c>
@@ -54749,7 +54750,7 @@
       <c r="F397" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G397" s="119" t="s">
+      <c r="G397" s="102" t="s">
         <v>328</v>
       </c>
       <c r="H397" s="19" t="s">
@@ -54860,7 +54861,7 @@
       </c>
       <c r="AP397" s="12"/>
     </row>
-    <row r="398" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" s="71">
         <v>46203</v>
       </c>
@@ -54879,7 +54880,7 @@
       <c r="F398" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G398" s="119" t="s">
+      <c r="G398" s="102" t="s">
         <v>328</v>
       </c>
       <c r="H398" s="19" t="s">
@@ -54990,7 +54991,7 @@
       </c>
       <c r="AP398" s="12"/>
     </row>
-    <row r="399" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="71">
         <v>46203</v>
       </c>
@@ -55009,7 +55010,7 @@
       <c r="F399" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G399" s="119" t="s">
+      <c r="G399" s="102" t="s">
         <v>328</v>
       </c>
       <c r="H399" s="19" t="s">
@@ -55117,7 +55118,7 @@
       </c>
       <c r="AP399" s="12"/>
     </row>
-    <row r="400" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="71">
         <v>46203</v>
       </c>
@@ -55136,7 +55137,7 @@
       <c r="F400" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G400" s="119" t="s">
+      <c r="G400" s="102" t="s">
         <v>328</v>
       </c>
       <c r="H400" s="19" t="s">
@@ -55244,7 +55245,7 @@
       </c>
       <c r="AP400" s="12"/>
     </row>
-    <row r="401" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="71">
         <v>46203</v>
       </c>
@@ -55263,7 +55264,7 @@
       <c r="F401" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G401" s="119" t="s">
+      <c r="G401" s="102" t="s">
         <v>328</v>
       </c>
       <c r="H401" s="19" t="s">
@@ -55371,7 +55372,7 @@
       </c>
       <c r="AP401" s="12"/>
     </row>
-    <row r="402" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="71">
         <v>46203</v>
       </c>
@@ -55390,7 +55391,7 @@
       <c r="F402" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G402" s="119" t="s">
+      <c r="G402" s="102" t="s">
         <v>328</v>
       </c>
       <c r="H402" s="19" t="s">
@@ -55498,7 +55499,7 @@
       </c>
       <c r="AP402" s="12"/>
     </row>
-    <row r="403" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" s="71">
         <v>46203</v>
       </c>
@@ -55517,7 +55518,7 @@
       <c r="F403" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G403" s="119" t="s">
+      <c r="G403" s="102" t="s">
         <v>328</v>
       </c>
       <c r="H403" s="19" t="s">
@@ -55625,7 +55626,7 @@
       </c>
       <c r="AP403" s="12"/>
     </row>
-    <row r="404" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" s="71">
         <v>46203</v>
       </c>
@@ -55644,7 +55645,7 @@
       <c r="F404" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G404" s="119" t="s">
+      <c r="G404" s="102" t="s">
         <v>328</v>
       </c>
       <c r="H404" s="19" t="s">
@@ -55752,7 +55753,7 @@
       </c>
       <c r="AP404" s="12"/>
     </row>
-    <row r="405" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" s="71">
         <v>46203</v>
       </c>
@@ -55771,7 +55772,7 @@
       <c r="F405" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="G405" s="119" t="s">
+      <c r="G405" s="102" t="s">
         <v>328</v>
       </c>
       <c r="H405" s="19" t="s">
@@ -55879,7 +55880,7 @@
       </c>
       <c r="AP405" s="12"/>
     </row>
-    <row r="406" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" s="17"/>
       <c r="C406" s="18"/>
       <c r="E406" s="6"/>
@@ -55976,7 +55977,7 @@
       </c>
       <c r="AP406" s="12"/>
     </row>
-    <row r="407" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" s="17"/>
       <c r="C407" s="18"/>
       <c r="E407" s="6"/>
@@ -56073,7 +56074,7 @@
       </c>
       <c r="AP407" s="12"/>
     </row>
-    <row r="408" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" s="17"/>
       <c r="C408" s="18"/>
       <c r="E408" s="6"/>
@@ -56170,7 +56171,7 @@
       </c>
       <c r="AP408" s="12"/>
     </row>
-    <row r="409" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" s="17"/>
       <c r="C409" s="18"/>
       <c r="E409" s="6"/>
@@ -56267,7 +56268,7 @@
       </c>
       <c r="AP409" s="12"/>
     </row>
-    <row r="410" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="17"/>
       <c r="C410" s="18"/>
       <c r="E410" s="6"/>
@@ -56364,7 +56365,7 @@
       </c>
       <c r="AP410" s="12"/>
     </row>
-    <row r="411" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="17"/>
       <c r="C411" s="18"/>
       <c r="E411" s="6"/>
@@ -56461,7 +56462,7 @@
       </c>
       <c r="AP411" s="12"/>
     </row>
-    <row r="412" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="17"/>
       <c r="C412" s="18"/>
       <c r="E412" s="6"/>
@@ -56558,7 +56559,7 @@
       </c>
       <c r="AP412" s="12"/>
     </row>
-    <row r="413" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="17"/>
       <c r="C413" s="18"/>
       <c r="E413" s="6"/>
@@ -56655,7 +56656,7 @@
       </c>
       <c r="AP413" s="12"/>
     </row>
-    <row r="414" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" s="17"/>
       <c r="C414" s="18"/>
       <c r="E414" s="6"/>
@@ -56752,7 +56753,7 @@
       </c>
       <c r="AP414" s="12"/>
     </row>
-    <row r="415" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" s="17"/>
       <c r="C415" s="18"/>
       <c r="E415" s="6"/>
@@ -56849,7 +56850,7 @@
       </c>
       <c r="AP415" s="12"/>
     </row>
-    <row r="416" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="17"/>
       <c r="C416" s="18"/>
       <c r="E416" s="6"/>
@@ -56946,7 +56947,7 @@
       </c>
       <c r="AP416" s="12"/>
     </row>
-    <row r="417" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" s="17"/>
       <c r="C417" s="18"/>
       <c r="E417" s="6"/>
@@ -57043,7 +57044,7 @@
       </c>
       <c r="AP417" s="12"/>
     </row>
-    <row r="418" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" s="17"/>
       <c r="C418" s="18"/>
       <c r="E418" s="6"/>
@@ -57140,7 +57141,7 @@
       </c>
       <c r="AP418" s="12"/>
     </row>
-    <row r="419" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" s="17"/>
       <c r="C419" s="18"/>
       <c r="E419" s="6"/>
@@ -57237,7 +57238,7 @@
       </c>
       <c r="AP419" s="12"/>
     </row>
-    <row r="420" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" s="17"/>
       <c r="C420" s="18"/>
       <c r="E420" s="6"/>
@@ -57334,7 +57335,7 @@
       </c>
       <c r="AP420" s="12"/>
     </row>
-    <row r="421" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" s="17"/>
       <c r="C421" s="18"/>
       <c r="E421" s="6"/>
@@ -57431,7 +57432,7 @@
       </c>
       <c r="AP421" s="12"/>
     </row>
-    <row r="422" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" s="17"/>
       <c r="C422" s="18"/>
       <c r="E422" s="6"/>
@@ -57528,7 +57529,7 @@
       </c>
       <c r="AP422" s="12"/>
     </row>
-    <row r="423" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" s="17"/>
       <c r="C423" s="18"/>
       <c r="E423" s="6"/>
@@ -57625,7 +57626,7 @@
       </c>
       <c r="AP423" s="12"/>
     </row>
-    <row r="424" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" s="17"/>
       <c r="C424" s="18"/>
       <c r="E424" s="6"/>
@@ -57722,7 +57723,7 @@
       </c>
       <c r="AP424" s="12"/>
     </row>
-    <row r="425" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" s="6"/>
       <c r="C425" s="6"/>
       <c r="E425" s="6"/>
@@ -58014,6 +58015,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP425" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="Zeshan"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="10" showButton="0"/>
     <filterColumn colId="11" showButton="0"/>
     <filterColumn colId="12" showButton="0"/>
@@ -58028,14 +58034,13 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -58048,13 +58053,14 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58080,22 +58086,22 @@
   <sheetData>
     <row r="3" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="4" spans="4:8" ht="22.5" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="D4" s="113" t="s">
+      <c r="D4" s="114" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="116"/>
     </row>
     <row r="5" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D5" s="22" t="s">
         <v>355</v>
       </c>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
     </row>
     <row r="6" spans="4:8" x14ac:dyDescent="0.35">
       <c r="D6" s="23" t="s">
@@ -58658,10 +58664,10 @@
       </c>
     </row>
     <row r="31" spans="3:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C31" s="117" t="s">
+      <c r="C31" s="118" t="s">
         <v>60</v>
       </c>
-      <c r="D31" s="118"/>
+      <c r="D31" s="119"/>
       <c r="E31" s="50">
         <f>SUM(E24:E30)</f>
         <v>8000</v>

--- a/june 2026/STT Report Elite Marketing (20-06-26) (1).xlsx
+++ b/june 2026/STT Report Elite Marketing (20-06-26) (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\june 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B97DF1D-E414-4821-B1B7-96792AA30571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C781536D-34A5-4B4D-87AD-5C2D7B3E905F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2521" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="558">
   <si>
     <t>Date</t>
   </si>
@@ -1692,6 +1692,18 @@
   <si>
     <t>Youhaba Abad</t>
   </si>
+  <si>
+    <t xml:space="preserve">zahid </t>
+  </si>
+  <si>
+    <t>Total pcs</t>
+  </si>
+  <si>
+    <t>ctns</t>
+  </si>
+  <si>
+    <t>Umair Rehan</t>
+  </si>
 </sst>
 </file>
 
@@ -2596,22 +2608,22 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2623,11 +2635,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2966,7 +2978,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AP431"/>
+  <dimension ref="A1:AP443"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -3008,44 +3020,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="107" t="s">
+      <c r="A1" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="108" t="s">
+      <c r="D1" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="108" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="108" t="s">
+      <c r="E1" s="103" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="107" t="s">
+      <c r="G1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="108" t="s">
+      <c r="H1" s="103" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="56"/>
-      <c r="K1" s="107" t="s">
+      <c r="K1" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="112" t="s">
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
       <c r="S1" s="109" t="s">
         <v>10</v>
       </c>
@@ -3061,61 +3073,61 @@
       <c r="Y1" s="111"/>
       <c r="Z1" s="111"/>
       <c r="AA1" s="111"/>
-      <c r="AB1" s="105" t="s">
+      <c r="AB1" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="105" t="s">
+      <c r="AC1" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="105" t="s">
+      <c r="AD1" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="105" t="s">
+      <c r="AE1" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="105" t="s">
+      <c r="AF1" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="105" t="s">
+      <c r="AG1" s="107" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="65">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="105" t="s">
+      <c r="AI1" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="105" t="s">
+      <c r="AJ1" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="105" t="s">
+      <c r="AK1" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="105" t="s">
+      <c r="AL1" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="105" t="s">
+      <c r="AM1" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="103" t="s">
+      <c r="AN1" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="103" t="s">
+      <c r="AO1" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="105" t="s">
+      <c r="AP1" s="107" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="107"/>
-      <c r="B2" s="107"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="108"/>
+      <c r="A2" s="106"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="103"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -3171,23 +3183,23 @@
       <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="106"/>
-      <c r="AC2" s="106"/>
-      <c r="AD2" s="106"/>
-      <c r="AE2" s="106"/>
-      <c r="AF2" s="106"/>
-      <c r="AG2" s="106"/>
+      <c r="AB2" s="108"/>
+      <c r="AC2" s="108"/>
+      <c r="AD2" s="108"/>
+      <c r="AE2" s="108"/>
+      <c r="AF2" s="108"/>
+      <c r="AG2" s="108"/>
       <c r="AH2" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="106"/>
-      <c r="AJ2" s="106"/>
-      <c r="AK2" s="106"/>
-      <c r="AL2" s="106"/>
-      <c r="AM2" s="106"/>
-      <c r="AN2" s="104"/>
-      <c r="AO2" s="104"/>
-      <c r="AP2" s="106"/>
+      <c r="AI2" s="108"/>
+      <c r="AJ2" s="108"/>
+      <c r="AK2" s="108"/>
+      <c r="AL2" s="108"/>
+      <c r="AM2" s="108"/>
+      <c r="AN2" s="113"/>
+      <c r="AO2" s="113"/>
+      <c r="AP2" s="108"/>
     </row>
     <row r="3" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="71">
@@ -3737,7 +3749,7 @@
       <c r="AO6" s="6"/>
       <c r="AP6" s="12"/>
     </row>
-    <row r="7" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:42" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="71">
         <v>46175</v>
       </c>
@@ -3883,7 +3895,7 @@
       </c>
       <c r="AP7" s="12"/>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="71">
         <v>46175</v>
       </c>
@@ -4555,7 +4567,7 @@
       </c>
       <c r="AP12" s="12"/>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="71">
         <v>46176</v>
       </c>
@@ -4689,7 +4701,7 @@
       </c>
       <c r="AP13" s="12"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="71">
         <v>46176</v>
       </c>
@@ -9231,7 +9243,7 @@
       </c>
       <c r="AP47" s="12"/>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="71">
         <v>46211</v>
       </c>
@@ -9363,7 +9375,7 @@
       </c>
       <c r="AP48" s="12"/>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="71">
         <v>46211</v>
       </c>
@@ -9491,7 +9503,7 @@
       </c>
       <c r="AP49" s="12"/>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="71">
         <v>46211</v>
       </c>
@@ -9623,7 +9635,7 @@
       </c>
       <c r="AP50" s="12"/>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="71">
         <v>46211</v>
       </c>
@@ -10285,7 +10297,7 @@
       </c>
       <c r="AP55" s="12"/>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="71">
         <v>46212</v>
       </c>
@@ -10317,17 +10329,17 @@
         <v>20</v>
       </c>
       <c r="K56" s="20">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="L56" s="20">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="M56" s="20">
         <v>20</v>
       </c>
       <c r="N56" s="8">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>80</v>
       </c>
       <c r="O56" s="18">
         <v>5</v>
@@ -10344,15 +10356,15 @@
       </c>
       <c r="S56" s="18">
         <f t="shared" si="2"/>
-        <v>650</v>
+        <v>110</v>
       </c>
       <c r="T56" s="18">
         <f t="shared" ref="T56:T115" si="45">K56/10</f>
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="U56" s="18">
         <f t="shared" ref="U56:U115" si="46">L56/10</f>
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="V56" s="18">
         <f t="shared" ref="V56:V115" si="47">M56/10</f>
@@ -10360,7 +10372,7 @@
       </c>
       <c r="W56" s="8">
         <f t="shared" si="6"/>
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="X56" s="18">
         <f t="shared" ref="X56:X115" si="48">O56/10</f>
@@ -10389,14 +10401,14 @@
       </c>
       <c r="AE56" s="9">
         <f t="shared" si="11"/>
-        <v>80528.149999999994</v>
+        <v>12972.8</v>
       </c>
       <c r="AF56" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG56" s="10">
         <f t="shared" ref="AG56:AG115" si="51">AE56*AF56</f>
-        <v>5234.3297499999999</v>
+        <v>843.23199999999997</v>
       </c>
       <c r="AH56" s="64">
         <f t="shared" si="13"/>
@@ -10404,22 +10416,22 @@
       </c>
       <c r="AI56" s="9">
         <f t="shared" si="14"/>
-        <v>75293.82024999999</v>
+        <v>12129.567999999999</v>
       </c>
       <c r="AJ56" s="5">
         <v>0.18</v>
       </c>
       <c r="AK56" s="11">
         <f t="shared" si="15"/>
-        <v>13552.887644999997</v>
+        <v>2183.32224</v>
       </c>
       <c r="AL56" s="9">
         <f t="shared" si="16"/>
-        <v>88846.707894999985</v>
+        <v>14312.890239999999</v>
       </c>
       <c r="AP56" s="12"/>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="71">
         <v>46212</v>
       </c>
@@ -10553,7 +10565,7 @@
       </c>
       <c r="AP57" s="12"/>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="71">
         <v>46212</v>
       </c>
@@ -10687,7 +10699,7 @@
       </c>
       <c r="AP58" s="12"/>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="71">
         <v>46212</v>
       </c>
@@ -10821,7 +10833,7 @@
       </c>
       <c r="AP59" s="12"/>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="71">
         <v>46212</v>
       </c>
@@ -12693,7 +12705,7 @@
       </c>
       <c r="AP73" s="12"/>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="71">
         <v>46183</v>
       </c>
@@ -12827,7 +12839,7 @@
       </c>
       <c r="AP74" s="12"/>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="71">
         <v>46183</v>
       </c>
@@ -12961,7 +12973,7 @@
       </c>
       <c r="AP75" s="12"/>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="71">
         <v>46183</v>
       </c>
@@ -14429,7 +14441,7 @@
       </c>
       <c r="AP86" s="12"/>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="71">
         <v>46184</v>
       </c>
@@ -14563,7 +14575,7 @@
       </c>
       <c r="AP87" s="12"/>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="71">
         <v>46184</v>
       </c>
@@ -14697,7 +14709,7 @@
       </c>
       <c r="AP88" s="12"/>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="71">
         <v>46184</v>
       </c>
@@ -14831,7 +14843,7 @@
       </c>
       <c r="AP89" s="12"/>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="71">
         <v>46184</v>
       </c>
@@ -14965,7 +14977,7 @@
       </c>
       <c r="AP90" s="12"/>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="71">
         <v>46184</v>
       </c>
@@ -16293,7 +16305,7 @@
       </c>
       <c r="AP100" s="12"/>
     </row>
-    <row r="101" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="71">
         <v>46185</v>
       </c>
@@ -16427,7 +16439,7 @@
       </c>
       <c r="AP101" s="12"/>
     </row>
-    <row r="102" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="71">
         <v>46185</v>
       </c>
@@ -16561,7 +16573,7 @@
       </c>
       <c r="AP102" s="12"/>
     </row>
-    <row r="103" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="71">
         <v>46185</v>
       </c>
@@ -16695,7 +16707,7 @@
       </c>
       <c r="AP103" s="12"/>
     </row>
-    <row r="104" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="71">
         <v>46185</v>
       </c>
@@ -16829,7 +16841,7 @@
       </c>
       <c r="AP104" s="12"/>
     </row>
-    <row r="105" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="71">
         <v>46185</v>
       </c>
@@ -17095,7 +17107,7 @@
       </c>
       <c r="AP106" s="12"/>
     </row>
-    <row r="107" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="71">
         <v>46186</v>
       </c>
@@ -17229,7 +17241,7 @@
       </c>
       <c r="AP107" s="12"/>
     </row>
-    <row r="108" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="71">
         <v>46186</v>
       </c>
@@ -17363,7 +17375,7 @@
       </c>
       <c r="AP108" s="12"/>
     </row>
-    <row r="109" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="71">
         <v>46186</v>
       </c>
@@ -17497,7 +17509,7 @@
       </c>
       <c r="AP109" s="12"/>
     </row>
-    <row r="110" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="71">
         <v>46186</v>
       </c>
@@ -22177,7 +22189,7 @@
       </c>
       <c r="AP144" s="12"/>
     </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="71">
         <v>46189</v>
       </c>
@@ -22311,7 +22323,7 @@
       </c>
       <c r="AP145" s="12"/>
     </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="71">
         <v>46189</v>
       </c>
@@ -22445,7 +22457,7 @@
       </c>
       <c r="AP146" s="12"/>
     </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="71">
         <v>46189</v>
       </c>
@@ -22579,7 +22591,7 @@
       </c>
       <c r="AP147" s="12"/>
     </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="71">
         <v>46189</v>
       </c>
@@ -22713,7 +22725,7 @@
       </c>
       <c r="AP148" s="12"/>
     </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="71">
         <v>46189</v>
       </c>
@@ -22847,7 +22859,7 @@
       </c>
       <c r="AP149" s="12"/>
     </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="71">
         <v>46189</v>
       </c>
@@ -22981,7 +22993,7 @@
       </c>
       <c r="AP150" s="12"/>
     </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="71">
         <v>46189</v>
       </c>
@@ -31069,7 +31081,7 @@
       </c>
       <c r="AP211" s="12"/>
     </row>
-    <row r="212" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="71">
         <v>46192</v>
       </c>
@@ -31201,7 +31213,7 @@
       </c>
       <c r="AP212" s="12"/>
     </row>
-    <row r="213" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="71">
         <v>46192</v>
       </c>
@@ -33313,7 +33325,7 @@
       </c>
       <c r="AP228" s="12"/>
     </row>
-    <row r="229" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="71">
         <v>46193</v>
       </c>
@@ -33447,7 +33459,7 @@
       </c>
       <c r="AP229" s="12"/>
     </row>
-    <row r="230" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="71">
         <v>46193</v>
       </c>
@@ -33581,7 +33593,7 @@
       </c>
       <c r="AP230" s="12"/>
     </row>
-    <row r="231" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="71">
         <v>46193</v>
       </c>
@@ -33715,7 +33727,7 @@
       </c>
       <c r="AP231" s="12"/>
     </row>
-    <row r="232" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="71">
         <v>46193</v>
       </c>
@@ -33849,7 +33861,7 @@
       </c>
       <c r="AP232" s="12"/>
     </row>
-    <row r="233" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="71">
         <v>46193</v>
       </c>
@@ -33983,7 +33995,7 @@
       </c>
       <c r="AP233" s="12"/>
     </row>
-    <row r="234" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="71">
         <v>46193</v>
       </c>
@@ -38317,11 +38329,11 @@
         <v>18</v>
       </c>
       <c r="M267" s="18">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="N267" s="8">
         <f t="shared" si="121"/>
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="O267" s="20">
         <v>15</v>
@@ -38338,7 +38350,7 @@
       </c>
       <c r="S267" s="18">
         <f t="shared" si="119"/>
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="T267" s="18">
         <f t="shared" si="122"/>
@@ -38350,11 +38362,11 @@
       </c>
       <c r="V267" s="18">
         <f t="shared" si="124"/>
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W267" s="8">
         <f t="shared" ref="W267:W330" si="129">N267/10</f>
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="X267" s="18">
         <f t="shared" si="125"/>
@@ -38383,14 +38395,14 @@
       </c>
       <c r="AE267" s="9">
         <f t="shared" ref="AE267:AE330" si="131">(J267*AB267)+(N267*AC267)+(AD267*S267)</f>
-        <v>9273.7200000000012</v>
+        <v>7021.875</v>
       </c>
       <c r="AF267" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG267" s="10">
         <f t="shared" si="128"/>
-        <v>602.79180000000008</v>
+        <v>456.421875</v>
       </c>
       <c r="AH267" s="64">
         <f t="shared" ref="AH267:AH330" si="132">(AB267*J267)*$AH$1</f>
@@ -38398,18 +38410,18 @@
       </c>
       <c r="AI267" s="9">
         <f t="shared" ref="AI267:AI330" si="133">AE267-AG267</f>
-        <v>8670.9282000000003</v>
+        <v>6565.453125</v>
       </c>
       <c r="AJ267" s="5">
         <v>0.18</v>
       </c>
       <c r="AK267" s="11">
         <f t="shared" ref="AK267:AK330" si="134">AI267*AJ267</f>
-        <v>1560.7670760000001</v>
+        <v>1181.7815625000001</v>
       </c>
       <c r="AL267" s="9">
         <f t="shared" ref="AL267:AL330" si="135">AI267+AK267</f>
-        <v>10231.695276</v>
+        <v>7747.2346875000003</v>
       </c>
       <c r="AP267" s="12"/>
     </row>
@@ -38448,7 +38460,9 @@
       <c r="L268" s="18">
         <v>20</v>
       </c>
-      <c r="M268" s="20"/>
+      <c r="M268" s="18">
+        <v>0</v>
+      </c>
       <c r="N268" s="8">
         <f t="shared" si="121"/>
         <v>40</v>
@@ -38568,7 +38582,9 @@
       <c r="J269" s="55"/>
       <c r="K269" s="20"/>
       <c r="L269" s="20"/>
-      <c r="M269" s="20"/>
+      <c r="M269" s="18">
+        <v>0</v>
+      </c>
       <c r="N269" s="8">
         <f t="shared" si="121"/>
         <v>0</v>
@@ -38698,12 +38714,12 @@
       <c r="L270" s="20">
         <v>6</v>
       </c>
-      <c r="M270" s="20">
-        <v>6</v>
+      <c r="M270" s="18">
+        <v>0</v>
       </c>
       <c r="N270" s="8">
         <f t="shared" si="121"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="O270" s="18"/>
       <c r="P270" s="18"/>
@@ -38714,7 +38730,7 @@
       </c>
       <c r="S270" s="18">
         <f t="shared" si="119"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T270" s="18">
         <f t="shared" si="122"/>
@@ -38726,11 +38742,11 @@
       </c>
       <c r="V270" s="18">
         <f t="shared" si="124"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W270" s="8">
         <f t="shared" si="129"/>
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="X270" s="18">
         <f t="shared" si="125"/>
@@ -38759,14 +38775,14 @@
       </c>
       <c r="AE270" s="9">
         <f t="shared" si="131"/>
-        <v>2251.8449999999998</v>
+        <v>1501.23</v>
       </c>
       <c r="AF270" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG270" s="10">
         <f t="shared" si="128"/>
-        <v>146.36992499999999</v>
+        <v>97.579950000000011</v>
       </c>
       <c r="AH270" s="64">
         <f t="shared" si="132"/>
@@ -38774,18 +38790,18 @@
       </c>
       <c r="AI270" s="9">
         <f t="shared" si="133"/>
-        <v>2105.4750749999998</v>
+        <v>1403.65005</v>
       </c>
       <c r="AJ270" s="5">
         <v>0.18</v>
       </c>
       <c r="AK270" s="11">
         <f t="shared" si="134"/>
-        <v>378.98551349999997</v>
+        <v>252.65700899999999</v>
       </c>
       <c r="AL270" s="9">
         <f t="shared" si="135"/>
-        <v>2484.4605884999996</v>
+        <v>1656.307059</v>
       </c>
       <c r="AP270" s="12"/>
     </row>
@@ -38825,28 +38841,28 @@
         <v>80</v>
       </c>
       <c r="M271" s="18">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="N271" s="8">
         <f t="shared" si="121"/>
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="O271" s="18">
         <v>80</v>
       </c>
       <c r="P271" s="18">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Q271" s="20">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="R271" s="8">
         <f t="shared" si="120"/>
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="S271" s="18">
         <f t="shared" si="119"/>
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="T271" s="18">
         <f t="shared" si="122"/>
@@ -38858,11 +38874,11 @@
       </c>
       <c r="V271" s="18">
         <f t="shared" si="124"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W271" s="8">
         <f t="shared" si="129"/>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="X271" s="18">
         <f t="shared" si="125"/>
@@ -38870,15 +38886,15 @@
       </c>
       <c r="Y271" s="18">
         <f t="shared" si="126"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z271" s="18">
         <f t="shared" si="127"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AA271" s="8">
         <f t="shared" si="130"/>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AB271" s="8">
         <v>39.270000000000003</v>
@@ -38891,14 +38907,14 @@
       </c>
       <c r="AE271" s="9">
         <f t="shared" si="131"/>
-        <v>47458.2</v>
+        <v>31638.799999999999</v>
       </c>
       <c r="AF271" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG271" s="10">
         <f t="shared" si="128"/>
-        <v>3084.7829999999999</v>
+        <v>2056.5219999999999</v>
       </c>
       <c r="AH271" s="64">
         <f t="shared" si="132"/>
@@ -38906,18 +38922,18 @@
       </c>
       <c r="AI271" s="9">
         <f t="shared" si="133"/>
-        <v>44373.416999999994</v>
+        <v>29582.277999999998</v>
       </c>
       <c r="AJ271" s="5">
         <v>0.18</v>
       </c>
       <c r="AK271" s="11">
         <f t="shared" si="134"/>
-        <v>7987.2150599999986</v>
+        <v>5324.8100399999994</v>
       </c>
       <c r="AL271" s="9">
         <f t="shared" si="135"/>
-        <v>52360.632059999989</v>
+        <v>34907.088039999995</v>
       </c>
       <c r="AP271" s="12"/>
     </row>
@@ -38952,7 +38968,9 @@
       <c r="J272" s="55"/>
       <c r="K272" s="18"/>
       <c r="L272" s="18"/>
-      <c r="M272" s="18"/>
+      <c r="M272" s="18">
+        <v>0</v>
+      </c>
       <c r="N272" s="8">
         <f t="shared" si="121"/>
         <v>0</v>
@@ -39045,7 +39063,7 @@
       </c>
       <c r="AP272" s="12"/>
     </row>
-    <row r="273" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="71">
         <v>46195</v>
       </c>
@@ -39169,7 +39187,7 @@
       </c>
       <c r="AP273" s="12"/>
     </row>
-    <row r="274" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="71">
         <v>46195</v>
       </c>
@@ -39291,7 +39309,7 @@
       </c>
       <c r="AP274" s="12"/>
     </row>
-    <row r="275" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="71">
         <v>46195</v>
       </c>
@@ -39413,7 +39431,7 @@
       </c>
       <c r="AP275" s="12"/>
     </row>
-    <row r="276" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="71">
         <v>46195</v>
       </c>
@@ -39539,7 +39557,7 @@
       </c>
       <c r="AP276" s="12"/>
     </row>
-    <row r="277" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="71">
         <v>46195</v>
       </c>
@@ -39661,7 +39679,7 @@
       </c>
       <c r="AP277" s="12"/>
     </row>
-    <row r="278" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="71">
         <v>46195</v>
       </c>
@@ -39783,7 +39801,7 @@
       </c>
       <c r="AP278" s="12"/>
     </row>
-    <row r="279" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="71">
         <v>46195</v>
       </c>
@@ -39905,7 +39923,7 @@
       </c>
       <c r="AP279" s="12"/>
     </row>
-    <row r="280" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="71">
         <v>46195</v>
       </c>
@@ -40450,7 +40468,9 @@
       <c r="J284" s="55"/>
       <c r="K284" s="18"/>
       <c r="L284" s="18"/>
-      <c r="M284" s="18"/>
+      <c r="M284" s="18">
+        <v>0</v>
+      </c>
       <c r="N284" s="8">
         <f t="shared" si="121"/>
         <v>0</v>
@@ -40583,11 +40603,11 @@
         <v>14</v>
       </c>
       <c r="M285" s="18">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N285" s="8">
         <f t="shared" si="121"/>
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O285" s="18"/>
       <c r="P285" s="20"/>
@@ -40598,7 +40618,7 @@
       </c>
       <c r="S285" s="18">
         <f t="shared" si="119"/>
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="T285" s="18">
         <f t="shared" si="122"/>
@@ -40610,11 +40630,11 @@
       </c>
       <c r="V285" s="18">
         <f t="shared" si="124"/>
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W285" s="8">
         <f t="shared" si="129"/>
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="X285" s="18">
         <f t="shared" si="125"/>
@@ -40643,14 +40663,14 @@
       </c>
       <c r="AE285" s="9">
         <f t="shared" si="131"/>
-        <v>9480.5</v>
+        <v>7979.27</v>
       </c>
       <c r="AF285" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG285" s="10">
         <f t="shared" si="128"/>
-        <v>616.23250000000007</v>
+        <v>518.65255000000002</v>
       </c>
       <c r="AH285" s="64">
         <f t="shared" si="132"/>
@@ -40658,18 +40678,18 @@
       </c>
       <c r="AI285" s="9">
         <f t="shared" si="133"/>
-        <v>8864.2674999999999</v>
+        <v>7460.6174500000006</v>
       </c>
       <c r="AJ285" s="5">
         <v>0.18</v>
       </c>
       <c r="AK285" s="11">
         <f t="shared" si="134"/>
-        <v>1595.5681499999998</v>
+        <v>1342.911141</v>
       </c>
       <c r="AL285" s="9">
         <f t="shared" si="135"/>
-        <v>10459.835649999999</v>
+        <v>8803.5285910000002</v>
       </c>
       <c r="AP285" s="12"/>
     </row>
@@ -40704,7 +40724,9 @@
       <c r="J286" s="55"/>
       <c r="K286" s="18"/>
       <c r="L286" s="18"/>
-      <c r="M286" s="18"/>
+      <c r="M286" s="18">
+        <v>0</v>
+      </c>
       <c r="N286" s="8">
         <f t="shared" si="121"/>
         <v>0</v>
@@ -40827,12 +40849,18 @@
       <c r="I287" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="J287" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="K287" s="18"/>
-      <c r="L287" s="20"/>
-      <c r="M287" s="18"/>
+      <c r="J287" s="55">
+        <v>0</v>
+      </c>
+      <c r="K287" s="18">
+        <v>0</v>
+      </c>
+      <c r="L287" s="20">
+        <v>0</v>
+      </c>
+      <c r="M287" s="18">
+        <v>0</v>
+      </c>
       <c r="N287" s="8">
         <f t="shared" si="121"/>
         <v>0</v>
@@ -40850,9 +40878,9 @@
         <f t="shared" si="120"/>
         <v>40</v>
       </c>
-      <c r="S287" s="18" t="e">
+      <c r="S287" s="18">
         <f t="shared" si="119"/>
-        <v>#VALUE!</v>
+        <v>40</v>
       </c>
       <c r="T287" s="18">
         <f t="shared" si="122"/>
@@ -40895,39 +40923,39 @@
       <c r="AD287" s="8">
         <v>72.64</v>
       </c>
-      <c r="AE287" s="9" t="e">
+      <c r="AE287" s="9">
         <f t="shared" si="131"/>
-        <v>#VALUE!</v>
+        <v>2905.6</v>
       </c>
       <c r="AF287" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AG287" s="10" t="e">
+      <c r="AG287" s="10">
         <f t="shared" si="128"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AH287" s="64" t="e">
+        <v>188.864</v>
+      </c>
+      <c r="AH287" s="64">
         <f t="shared" si="132"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AI287" s="9" t="e">
+        <v>0</v>
+      </c>
+      <c r="AI287" s="9">
         <f t="shared" si="133"/>
-        <v>#VALUE!</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ287" s="5">
         <v>0.18</v>
       </c>
-      <c r="AK287" s="11" t="e">
+      <c r="AK287" s="11">
         <f t="shared" si="134"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AL287" s="9" t="e">
+        <v>489.01247999999998</v>
+      </c>
+      <c r="AL287" s="9">
         <f t="shared" si="135"/>
-        <v>#VALUE!</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP287" s="12"/>
     </row>
-    <row r="288" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="71">
         <v>46196</v>
       </c>
@@ -41049,7 +41077,7 @@
       </c>
       <c r="AP288" s="12"/>
     </row>
-    <row r="289" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="71">
         <v>46196</v>
       </c>
@@ -41171,7 +41199,7 @@
       </c>
       <c r="AP289" s="12"/>
     </row>
-    <row r="290" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="71">
         <v>46196</v>
       </c>
@@ -41293,7 +41321,7 @@
       </c>
       <c r="AP290" s="12"/>
     </row>
-    <row r="291" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="71">
         <v>46196</v>
       </c>
@@ -41415,7 +41443,7 @@
       </c>
       <c r="AP291" s="12"/>
     </row>
-    <row r="292" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="71">
         <v>46196</v>
       </c>
@@ -41543,7 +41571,7 @@
       </c>
       <c r="AP292" s="12"/>
     </row>
-    <row r="293" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="71">
         <v>46196</v>
       </c>
@@ -41669,7 +41697,7 @@
       </c>
       <c r="AP293" s="12"/>
     </row>
-    <row r="294" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="71">
         <v>46196</v>
       </c>
@@ -41801,7 +41829,7 @@
       </c>
       <c r="AP294" s="12"/>
     </row>
-    <row r="295" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="71">
         <v>46196</v>
       </c>
@@ -42435,7 +42463,7 @@
       </c>
       <c r="AP299" s="12"/>
     </row>
-    <row r="300" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A300" s="71">
         <v>46197</v>
       </c>
@@ -42559,7 +42587,7 @@
       </c>
       <c r="AP300" s="12"/>
     </row>
-    <row r="301" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A301" s="71">
         <v>46197</v>
       </c>
@@ -42687,7 +42715,7 @@
       </c>
       <c r="AP301" s="12"/>
     </row>
-    <row r="302" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A302" s="71">
         <v>46197</v>
       </c>
@@ -43482,7 +43510,9 @@
       <c r="L308" s="20">
         <v>40</v>
       </c>
-      <c r="M308" s="20"/>
+      <c r="M308" s="18">
+        <v>0</v>
+      </c>
       <c r="N308" s="8">
         <f t="shared" si="121"/>
         <v>60</v>
@@ -43608,7 +43638,9 @@
       <c r="J309" s="55"/>
       <c r="K309" s="18"/>
       <c r="L309" s="18"/>
-      <c r="M309" s="18"/>
+      <c r="M309" s="18">
+        <v>0</v>
+      </c>
       <c r="N309" s="8">
         <f t="shared" si="121"/>
         <v>0</v>
@@ -43703,7 +43735,7 @@
       </c>
       <c r="AP309" s="12"/>
     </row>
-    <row r="310" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="71">
         <v>46197</v>
       </c>
@@ -43833,7 +43865,7 @@
       </c>
       <c r="AP310" s="12"/>
     </row>
-    <row r="311" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="71">
         <v>46197</v>
       </c>
@@ -43955,7 +43987,7 @@
       </c>
       <c r="AP311" s="12"/>
     </row>
-    <row r="312" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="71">
         <v>46197</v>
       </c>
@@ -44077,7 +44109,7 @@
       </c>
       <c r="AP312" s="12"/>
     </row>
-    <row r="313" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="71">
         <v>46197</v>
       </c>
@@ -44199,7 +44231,7 @@
       </c>
       <c r="AP313" s="12"/>
     </row>
-    <row r="314" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="71">
         <v>46197</v>
       </c>
@@ -44327,7 +44359,7 @@
       </c>
       <c r="AP314" s="12"/>
     </row>
-    <row r="315" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="71">
         <v>46197</v>
       </c>
@@ -44453,7 +44485,7 @@
       </c>
       <c r="AP315" s="12"/>
     </row>
-    <row r="316" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="71">
         <v>46197</v>
       </c>
@@ -44575,7 +44607,7 @@
       </c>
       <c r="AP316" s="12"/>
     </row>
-    <row r="317" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="71">
         <v>46197</v>
       </c>
@@ -44697,7 +44729,7 @@
       </c>
       <c r="AP317" s="12"/>
     </row>
-    <row r="318" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="71">
         <v>46197</v>
       </c>
@@ -47564,7 +47596,9 @@
       <c r="L340" s="18">
         <v>40</v>
       </c>
-      <c r="M340" s="18"/>
+      <c r="M340" s="18">
+        <v>0</v>
+      </c>
       <c r="N340" s="8">
         <f t="shared" si="145"/>
         <v>80</v>
@@ -47690,7 +47724,9 @@
       <c r="J341" s="55"/>
       <c r="K341" s="20"/>
       <c r="L341" s="20"/>
-      <c r="M341" s="20"/>
+      <c r="M341" s="18">
+        <v>0</v>
+      </c>
       <c r="N341" s="8">
         <f t="shared" si="145"/>
         <v>0</v>
@@ -47816,7 +47852,9 @@
       <c r="J342" s="55"/>
       <c r="K342" s="18"/>
       <c r="L342" s="18"/>
-      <c r="M342" s="20"/>
+      <c r="M342" s="18">
+        <v>0</v>
+      </c>
       <c r="N342" s="8">
         <f t="shared" si="145"/>
         <v>0</v>
@@ -47946,7 +47984,9 @@
       <c r="L343" s="20">
         <v>20</v>
       </c>
-      <c r="M343" s="20"/>
+      <c r="M343" s="18">
+        <v>0</v>
+      </c>
       <c r="N343" s="8">
         <f t="shared" si="145"/>
         <v>40</v>
@@ -48066,7 +48106,9 @@
       <c r="J344" s="55"/>
       <c r="K344" s="20"/>
       <c r="L344" s="20"/>
-      <c r="M344" s="20"/>
+      <c r="M344" s="18">
+        <v>0</v>
+      </c>
       <c r="N344" s="8">
         <f t="shared" si="145"/>
         <v>0</v>
@@ -48192,7 +48234,9 @@
       <c r="J345" s="55"/>
       <c r="K345" s="20"/>
       <c r="L345" s="20"/>
-      <c r="M345" s="20"/>
+      <c r="M345" s="18">
+        <v>0</v>
+      </c>
       <c r="N345" s="8">
         <f t="shared" si="145"/>
         <v>0</v>
@@ -48318,7 +48362,9 @@
       <c r="J346" s="55"/>
       <c r="K346" s="18"/>
       <c r="L346" s="18"/>
-      <c r="M346" s="20"/>
+      <c r="M346" s="18">
+        <v>0</v>
+      </c>
       <c r="N346" s="8">
         <f t="shared" si="145"/>
         <v>0</v>
@@ -48444,7 +48490,9 @@
       <c r="J347" s="55"/>
       <c r="K347" s="18"/>
       <c r="L347" s="20"/>
-      <c r="M347" s="20"/>
+      <c r="M347" s="18">
+        <v>0</v>
+      </c>
       <c r="N347" s="8">
         <f t="shared" si="145"/>
         <v>0</v>
@@ -48539,7 +48587,7 @@
       </c>
       <c r="AP347" s="12"/>
     </row>
-    <row r="348" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="71">
         <v>46202</v>
       </c>
@@ -48663,7 +48711,7 @@
       </c>
       <c r="AP348" s="12"/>
     </row>
-    <row r="349" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="71">
         <v>46202</v>
       </c>
@@ -51638,7 +51686,9 @@
       </c>
       <c r="K372" s="18"/>
       <c r="L372" s="18"/>
-      <c r="M372" s="18"/>
+      <c r="M372" s="18">
+        <v>0</v>
+      </c>
       <c r="N372" s="8">
         <f t="shared" si="145"/>
         <v>0</v>
@@ -51760,7 +51810,9 @@
       </c>
       <c r="K373" s="20"/>
       <c r="L373" s="20"/>
-      <c r="M373" s="18"/>
+      <c r="M373" s="18">
+        <v>0</v>
+      </c>
       <c r="N373" s="8">
         <f t="shared" si="145"/>
         <v>0</v>
@@ -51886,7 +51938,9 @@
       <c r="L374" s="18">
         <v>15</v>
       </c>
-      <c r="M374" s="18"/>
+      <c r="M374" s="18">
+        <v>0</v>
+      </c>
       <c r="N374" s="8">
         <f t="shared" si="145"/>
         <v>30</v>
@@ -52008,7 +52062,9 @@
       </c>
       <c r="K375" s="20"/>
       <c r="L375" s="20"/>
-      <c r="M375" s="20"/>
+      <c r="M375" s="18">
+        <v>0</v>
+      </c>
       <c r="N375" s="8">
         <f t="shared" si="145"/>
         <v>0</v>
@@ -52130,7 +52186,9 @@
       </c>
       <c r="K376" s="20"/>
       <c r="L376" s="20"/>
-      <c r="M376" s="20"/>
+      <c r="M376" s="18">
+        <v>0</v>
+      </c>
       <c r="N376" s="8">
         <f t="shared" si="145"/>
         <v>0</v>
@@ -52252,7 +52310,9 @@
       </c>
       <c r="K377" s="20"/>
       <c r="L377" s="20"/>
-      <c r="M377" s="20"/>
+      <c r="M377" s="18">
+        <v>0</v>
+      </c>
       <c r="N377" s="8">
         <f t="shared" si="145"/>
         <v>0</v>
@@ -52341,7 +52401,7 @@
       </c>
       <c r="AP377" s="12"/>
     </row>
-    <row r="378" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="71">
         <v>46203</v>
       </c>
@@ -52471,7 +52531,7 @@
       </c>
       <c r="AP378" s="12"/>
     </row>
-    <row r="379" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="71">
         <v>46203</v>
       </c>
@@ -52601,7 +52661,7 @@
       </c>
       <c r="AP379" s="12"/>
     </row>
-    <row r="380" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="71">
         <v>46203</v>
       </c>
@@ -52727,7 +52787,7 @@
       </c>
       <c r="AP380" s="12"/>
     </row>
-    <row r="381" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="71">
         <v>46203</v>
       </c>
@@ -52851,7 +52911,7 @@
       </c>
       <c r="AP381" s="12"/>
     </row>
-    <row r="382" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="71">
         <v>46203</v>
       </c>
@@ -52977,7 +53037,7 @@
       </c>
       <c r="AP382" s="12"/>
     </row>
-    <row r="383" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="71">
         <v>46203</v>
       </c>
@@ -53109,7 +53169,7 @@
       </c>
       <c r="AP383" s="12"/>
     </row>
-    <row r="384" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="71">
         <v>46203</v>
       </c>
@@ -53241,7 +53301,7 @@
       </c>
       <c r="AP384" s="12"/>
     </row>
-    <row r="385" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="71">
         <v>46203</v>
       </c>
@@ -53369,7 +53429,7 @@
       </c>
       <c r="AP385" s="12"/>
     </row>
-    <row r="386" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="71">
         <v>46203</v>
       </c>
@@ -53491,7 +53551,7 @@
       </c>
       <c r="AP386" s="12"/>
     </row>
-    <row r="387" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="71">
         <v>46203</v>
       </c>
@@ -53617,7 +53677,7 @@
       </c>
       <c r="AP387" s="12"/>
     </row>
-    <row r="388" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" s="71">
         <v>46203</v>
       </c>
@@ -53739,7 +53799,7 @@
       </c>
       <c r="AP388" s="12"/>
     </row>
-    <row r="389" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" s="71">
         <v>46203</v>
       </c>
@@ -53861,7 +53921,7 @@
       </c>
       <c r="AP389" s="12"/>
     </row>
-    <row r="390" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" s="71">
         <v>46203</v>
       </c>
@@ -53983,7 +54043,7 @@
       </c>
       <c r="AP390" s="12"/>
     </row>
-    <row r="391" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" s="71">
         <v>46203</v>
       </c>
@@ -54105,7 +54165,7 @@
       </c>
       <c r="AP391" s="12"/>
     </row>
-    <row r="392" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" s="71">
         <v>46203</v>
       </c>
@@ -54227,7 +54287,7 @@
       </c>
       <c r="AP392" s="12"/>
     </row>
-    <row r="393" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" s="71">
         <v>46203</v>
       </c>
@@ -54349,7 +54409,7 @@
       </c>
       <c r="AP393" s="12"/>
     </row>
-    <row r="394" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:42" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" s="71">
         <v>46203</v>
       </c>
@@ -57737,19 +57797,19 @@
       </c>
       <c r="K425" s="6">
         <f t="shared" si="177"/>
-        <v>17679</v>
+        <v>17409</v>
       </c>
       <c r="L425" s="6">
         <f t="shared" si="177"/>
-        <v>16923</v>
+        <v>16653</v>
       </c>
       <c r="M425" s="6">
         <f t="shared" si="177"/>
-        <v>17523</v>
+        <v>17407</v>
       </c>
       <c r="N425" s="6">
         <f t="shared" si="177"/>
-        <v>52125</v>
+        <v>51469</v>
       </c>
       <c r="O425" s="6">
         <f t="shared" si="177"/>
@@ -57757,35 +57817,35 @@
       </c>
       <c r="P425" s="6">
         <f t="shared" si="177"/>
-        <v>21651</v>
+        <v>21611</v>
       </c>
       <c r="Q425" s="6">
         <f t="shared" si="177"/>
-        <v>30027</v>
+        <v>29987</v>
       </c>
       <c r="R425" s="6">
         <f>SUM(R3:R424)</f>
-        <v>76900</v>
-      </c>
-      <c r="S425" s="6" t="e">
+        <v>76820</v>
+      </c>
+      <c r="S425" s="6">
         <f>SUM(S3:S424)</f>
-        <v>#VALUE!</v>
+        <v>133692</v>
       </c>
       <c r="T425" s="6">
         <f t="shared" si="177"/>
-        <v>1767.5</v>
+        <v>1740.5</v>
       </c>
       <c r="U425" s="6">
         <f t="shared" si="177"/>
-        <v>1692.0000000000002</v>
+        <v>1665</v>
       </c>
       <c r="V425" s="6">
         <f t="shared" si="177"/>
-        <v>1752.1499999999996</v>
+        <v>1740.5499999999997</v>
       </c>
       <c r="W425" s="6">
         <f t="shared" si="177"/>
-        <v>5211.6499999999996</v>
+        <v>5146.05</v>
       </c>
       <c r="X425" s="6">
         <f t="shared" si="177"/>
@@ -57793,43 +57853,43 @@
       </c>
       <c r="Y425" s="6">
         <f t="shared" si="177"/>
-        <v>2165.1</v>
+        <v>2161.1</v>
       </c>
       <c r="Z425" s="6">
         <f t="shared" si="177"/>
-        <v>3002.7000000000003</v>
+        <v>2998.7000000000003</v>
       </c>
       <c r="AA425" s="6">
         <f t="shared" si="177"/>
-        <v>7689.9999999999991</v>
+        <v>7681.9999999999991</v>
       </c>
       <c r="AB425" s="6"/>
       <c r="AC425" s="6"/>
       <c r="AD425" s="6"/>
-      <c r="AE425" s="6" t="e">
+      <c r="AE425" s="6">
         <f>SUM(AE3:AE424)</f>
-        <v>#VALUE!</v>
+        <v>12686587.102499973</v>
       </c>
       <c r="AF425" s="7"/>
-      <c r="AG425" s="6" t="e">
+      <c r="AG425" s="6">
         <f>SUM(AG3:AG424)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AH425" s="6" t="e">
+        <v>898818.61258750048</v>
+      </c>
+      <c r="AH425" s="6">
         <f>SUM(AH3:AH424)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AI425" s="6" t="e">
+        <v>9625.2733499999977</v>
+      </c>
+      <c r="AI425" s="6">
         <f>SUM(AI3:AI424)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AK425" s="6" t="e">
+        <v>11787699.767412491</v>
+      </c>
+      <c r="AK425" s="6">
         <f>SUM(AK3:AK424)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AL425" s="6" t="e">
+        <v>2121785.9581342461</v>
+      </c>
+      <c r="AL425" s="6">
         <f>SUM(AL3:AL424)</f>
-        <v>#VALUE!</v>
+        <v>13909485.725546744</v>
       </c>
       <c r="AP425" s="12"/>
     </row>
@@ -57910,19 +57970,19 @@
       </c>
       <c r="K429" s="62">
         <f t="shared" si="178"/>
-        <v>441.97500000000002</v>
+        <v>435.22500000000002</v>
       </c>
       <c r="L429" s="62">
         <f t="shared" si="178"/>
-        <v>423.07499999999999</v>
+        <v>416.32499999999999</v>
       </c>
       <c r="M429" s="62">
         <f t="shared" si="178"/>
-        <v>438.07499999999999</v>
+        <v>435.17500000000001</v>
       </c>
       <c r="N429" s="61">
         <f t="shared" si="178"/>
-        <v>1303.125</v>
+        <v>1286.7249999999999</v>
       </c>
       <c r="O429" s="62">
         <f t="shared" si="178"/>
@@ -57930,35 +57990,35 @@
       </c>
       <c r="P429" s="62">
         <f t="shared" si="178"/>
-        <v>541.27499999999998</v>
+        <v>540.27499999999998</v>
       </c>
       <c r="Q429" s="62">
         <f t="shared" si="178"/>
-        <v>750.67499999999995</v>
+        <v>749.67499999999995</v>
       </c>
       <c r="R429" s="61">
         <f t="shared" si="178"/>
-        <v>1922.5</v>
-      </c>
-      <c r="S429" s="80" t="e">
+        <v>1920.5</v>
+      </c>
+      <c r="S429" s="80">
         <f t="shared" si="178"/>
-        <v>#VALUE!</v>
+        <v>3342.3</v>
       </c>
       <c r="T429" s="80">
         <f t="shared" si="178"/>
-        <v>44.1875</v>
+        <v>43.512500000000003</v>
       </c>
       <c r="U429" s="80">
         <f t="shared" si="178"/>
-        <v>42.300000000000004</v>
+        <v>41.625</v>
       </c>
       <c r="V429" s="80">
         <f t="shared" si="178"/>
-        <v>43.803749999999994</v>
+        <v>43.513749999999995</v>
       </c>
       <c r="W429" s="80">
         <f t="shared" si="178"/>
-        <v>130.29124999999999</v>
+        <v>128.65125</v>
       </c>
       <c r="X429" s="80">
         <f t="shared" si="178"/>
@@ -57966,15 +58026,15 @@
       </c>
       <c r="Y429" s="80">
         <f t="shared" si="178"/>
-        <v>54.127499999999998</v>
+        <v>54.027499999999996</v>
       </c>
       <c r="Z429" s="80">
         <f t="shared" si="178"/>
-        <v>75.06750000000001</v>
+        <v>74.967500000000001</v>
       </c>
       <c r="AA429" s="80">
         <f t="shared" si="178"/>
-        <v>192.24999999999997</v>
+        <v>192.04999999999998</v>
       </c>
       <c r="AB429" s="81"/>
       <c r="AC429" s="57">
@@ -57985,9 +58045,9 @@
         <f t="shared" si="178"/>
         <v>0</v>
       </c>
-      <c r="AE429" s="57" t="e">
+      <c r="AE429" s="57">
         <f t="shared" si="178"/>
-        <v>#VALUE!</v>
+        <v>317164.6775624993</v>
       </c>
       <c r="AF429" s="57">
         <f t="shared" si="178"/>
@@ -58005,19 +58065,153 @@
       <c r="AP429" s="57"/>
     </row>
     <row r="431" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="S431" s="79" t="e">
+      <c r="S431" s="79">
         <f>S429+W429+AA429</f>
-        <v>#VALUE!</v>
+        <v>3663.0012500000003</v>
       </c>
       <c r="X431" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="433" spans="7:14" x14ac:dyDescent="0.35">
+      <c r="H433" t="s">
+        <v>555</v>
+      </c>
+      <c r="I433" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="434" spans="7:14" x14ac:dyDescent="0.35">
+      <c r="G434" t="s">
+        <v>554</v>
+      </c>
+      <c r="H434">
+        <v>3574</v>
+      </c>
+      <c r="I434">
+        <f>H434/40</f>
+        <v>89.35</v>
+      </c>
+      <c r="L434">
+        <f>1394+19</f>
+        <v>1413</v>
+      </c>
+      <c r="N434">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="435" spans="7:14" x14ac:dyDescent="0.35">
+      <c r="G435" t="s">
+        <v>89</v>
+      </c>
+      <c r="H435">
+        <v>11891</v>
+      </c>
+      <c r="I435">
+        <f t="shared" ref="I435:I443" si="179">H435/40</f>
+        <v>297.27499999999998</v>
+      </c>
+      <c r="L435">
+        <f>L434/40</f>
+        <v>35.325000000000003</v>
+      </c>
+      <c r="N435">
+        <f>N434/40</f>
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="436" spans="7:14" x14ac:dyDescent="0.35">
+      <c r="G436" t="s">
+        <v>90</v>
+      </c>
+      <c r="H436">
+        <v>3065</v>
+      </c>
+      <c r="I436">
+        <f t="shared" si="179"/>
+        <v>76.625</v>
+      </c>
+    </row>
+    <row r="437" spans="7:14" x14ac:dyDescent="0.35">
+      <c r="G437" t="s">
+        <v>102</v>
+      </c>
+      <c r="H437">
+        <v>6474</v>
+      </c>
+      <c r="I437">
+        <f t="shared" si="179"/>
+        <v>161.85</v>
+      </c>
+    </row>
+    <row r="438" spans="7:14" x14ac:dyDescent="0.35">
+      <c r="G438" t="s">
+        <v>104</v>
+      </c>
+      <c r="H438">
+        <v>5386</v>
+      </c>
+      <c r="I438">
+        <f t="shared" si="179"/>
+        <v>134.65</v>
+      </c>
+    </row>
+    <row r="439" spans="7:14" x14ac:dyDescent="0.35">
+      <c r="G439" t="s">
+        <v>557</v>
+      </c>
+      <c r="H439">
+        <v>2456</v>
+      </c>
+      <c r="I439">
+        <f t="shared" si="179"/>
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="440" spans="7:14" x14ac:dyDescent="0.35">
+      <c r="G440" t="s">
+        <v>446</v>
+      </c>
+      <c r="H440">
+        <v>138</v>
+      </c>
+      <c r="I440">
+        <f t="shared" si="179"/>
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="441" spans="7:14" x14ac:dyDescent="0.35">
+      <c r="H441">
+        <v>0</v>
+      </c>
+      <c r="I441">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="7:14" x14ac:dyDescent="0.35">
+      <c r="H442">
+        <v>0</v>
+      </c>
+      <c r="I442">
+        <f t="shared" si="179"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="7:14" x14ac:dyDescent="0.35">
+      <c r="H443">
+        <v>0</v>
+      </c>
+      <c r="I443">
+        <f t="shared" si="179"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AP425" xr:uid="{4909E717-3884-4AA3-A82A-69FACD0ADABD}">
     <filterColumn colId="7">
       <filters>
-        <filter val="Zeshan"/>
+        <filter val="Umer"/>
       </filters>
     </filterColumn>
     <filterColumn colId="10" showButton="0"/>
@@ -58034,13 +58228,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -58053,14 +58248,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -58132,11 +58326,11 @@
       </c>
       <c r="G7" s="29">
         <f>'STT Report'!Q429+'STT Report'!Z429</f>
-        <v>825.74249999999995</v>
+        <v>824.64249999999993</v>
       </c>
       <c r="H7" s="30">
         <f>E7+F7-G7</f>
-        <v>103.35750000000007</v>
+        <v>104.4575000000001</v>
       </c>
     </row>
     <row r="8" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -58151,11 +58345,11 @@
       </c>
       <c r="G8" s="29">
         <f>'STT Report'!P429+'STT Report'!Y429</f>
-        <v>595.40249999999992</v>
+        <v>594.30250000000001</v>
       </c>
       <c r="H8" s="30">
         <f>E8+F8-G8</f>
-        <v>83.697500000000105</v>
+        <v>84.797500000000014</v>
       </c>
     </row>
     <row r="9" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -58191,11 +58385,11 @@
       </c>
       <c r="G10" s="35">
         <f>SUM(G7:G9)</f>
-        <v>2114.75</v>
+        <v>2112.5500000000002</v>
       </c>
       <c r="H10" s="36">
         <f>SUM(H7:H9)</f>
-        <v>361.75000000000011</v>
+        <v>363.95000000000005</v>
       </c>
     </row>
     <row r="11" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -58270,11 +58464,11 @@
       </c>
       <c r="G15" s="29">
         <f>'STT Report'!M429+'STT Report'!V429</f>
-        <v>481.87874999999997</v>
+        <v>478.68875000000003</v>
       </c>
       <c r="H15" s="30">
         <f>E15+F15-G15</f>
-        <v>-96.778749999999945</v>
+        <v>-93.588750000000005</v>
       </c>
     </row>
     <row r="16" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -58289,11 +58483,11 @@
       </c>
       <c r="G16" s="29">
         <f>'STT Report'!L429+'STT Report'!U429</f>
-        <v>465.375</v>
+        <v>457.95</v>
       </c>
       <c r="H16" s="30">
         <f>E16+F16-G16</f>
-        <v>168.625</v>
+        <v>176.05</v>
       </c>
     </row>
     <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.45">
@@ -58308,11 +58502,11 @@
       </c>
       <c r="G17" s="29">
         <f>'STT Report'!K429+'STT Report'!T429</f>
-        <v>486.16250000000002</v>
+        <v>478.73750000000001</v>
       </c>
       <c r="H17" s="30">
         <f>E17+F17-G17</f>
-        <v>142.53750000000002</v>
+        <v>149.96250000000003</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -58329,11 +58523,11 @@
       </c>
       <c r="G18" s="35">
         <f>SUM(G15:G17)</f>
-        <v>1433.41625</v>
+        <v>1415.37625</v>
       </c>
       <c r="H18" s="36">
         <f>SUM(H15:H17)</f>
-        <v>214.38375000000008</v>
+        <v>232.42375000000004</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -58350,11 +58544,11 @@
       </c>
       <c r="G19" s="38">
         <f>G10+G14+G18</f>
-        <v>3723.24125</v>
+        <v>3703.0012500000003</v>
       </c>
       <c r="H19" s="40">
         <f>H10+H14+H18</f>
-        <v>2275.9587500000002</v>
+        <v>2296.19875</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">
